--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -556,10 +556,10 @@
         <v>280</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>7560000</v>
+        <v>7566072.289156641</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1316,10 +1316,10 @@
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>15403.521040462</v>
+        <v>15403.521104651</v>
       </c>
       <c r="O23" t="n">
-        <v>462105.63121386</v>
+        <v>462105.63313953</v>
       </c>
       <c r="P23" t="n">
         <v>33500</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.367141182</v>
+        <v>7053243.366335525</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.1018941423</v>
+        <v>924366.8113728163</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.289812034</v>
+        <v>1385850.046287961</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4709258607</v>
+        <v>35654.4710214234</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5367,10 +5367,10 @@
         <v>50</v>
       </c>
       <c r="N113" t="n">
-        <v>2069.4655430712</v>
+        <v>2069.4655178908</v>
       </c>
       <c r="O113" t="n">
-        <v>103473.27715356</v>
+        <v>103473.27589454</v>
       </c>
       <c r="P113" t="n">
         <v>6500</v>
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3926522495</v>
+        <v>836853.3924435937</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -8932,10 +8932,10 @@
         <v>216</v>
       </c>
       <c r="N193" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O193" t="n">
-        <v>449146.832093532</v>
+        <v>449146.8175415256</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -9390,10 +9390,10 @@
         <v>2</v>
       </c>
       <c r="N203" t="n">
-        <v>1906.1790510949</v>
+        <v>1906.1788059701</v>
       </c>
       <c r="O203" t="n">
-        <v>3812.3581021898</v>
+        <v>3812.3576119402</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -10505,10 +10505,10 @@
         <v>1</v>
       </c>
       <c r="N227" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="O227" t="n">
-        <v>1690.8700092894</v>
+        <v>1690.870009298</v>
       </c>
       <c r="P227" t="n">
         <v>3000</v>
@@ -11217,10 +11217,10 @@
         <v>11930</v>
       </c>
       <c r="N242" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O242" t="n">
-        <v>8396272.409177136</v>
+        <v>8397136.334312502</v>
       </c>
       <c r="P242" t="n">
         <v>900</v>
@@ -14870,10 +14870,10 @@
         <v>1000</v>
       </c>
       <c r="N318" t="n">
-        <v>1783.7988761992</v>
+        <v>1783.7988756856</v>
       </c>
       <c r="O318" t="n">
-        <v>1783798.8761992</v>
+        <v>1783798.8756856</v>
       </c>
       <c r="P318" t="n">
         <v>1500</v>
@@ -15927,10 +15927,10 @@
         <v>50</v>
       </c>
       <c r="N340" t="n">
-        <v>8919.16</v>
+        <v>8975.6103797468</v>
       </c>
       <c r="O340" t="n">
-        <v>445958</v>
+        <v>448780.51898734</v>
       </c>
       <c r="P340" t="n">
         <v>10000</v>
@@ -17529,10 +17529,10 @@
         <v>455</v>
       </c>
       <c r="N373" t="n">
-        <v>315.02726865672</v>
+        <v>315.02740121581</v>
       </c>
       <c r="O373" t="n">
-        <v>143337.4072388076</v>
+        <v>143337.4675531936</v>
       </c>
       <c r="P373" t="n">
         <v>2200</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>280</v>
       </c>
       <c r="N4" t="n">
-        <v>27021.686746988</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>7566072.289156641</v>
+        <v>7560000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2551438323</v>
+        <v>2582.2551367187</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.201462722</v>
+        <v>2360181.194960892</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8959810174</v>
+        <v>5216.895979825</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.366335525</v>
+        <v>7053243.364723399</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608348592</v>
+        <v>3158.8608362663</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.44686987</v>
+        <v>10771715.45166808</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -3679,10 +3679,10 @@
         <v>320</v>
       </c>
       <c r="N76" t="n">
-        <v>3841.6250103093</v>
+        <v>3841.6250258532</v>
       </c>
       <c r="O76" t="n">
-        <v>1229320.003298976</v>
+        <v>1229320.008273024</v>
       </c>
       <c r="P76" t="n">
         <v>6900</v>
@@ -3774,10 +3774,10 @@
         <v>514</v>
       </c>
       <c r="N78" t="n">
-        <v>2694.823125</v>
+        <v>2694.8231119545</v>
       </c>
       <c r="O78" t="n">
-        <v>1385139.08625</v>
+        <v>1385139.079544613</v>
       </c>
       <c r="P78" t="n">
         <v>4900</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3596.7580209059</v>
+        <v>3594.2532489451</v>
       </c>
       <c r="O84" t="n">
-        <v>924366.8113728163</v>
+        <v>923723.0849788907</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.766707533</v>
+        <v>4371.1712622683</v>
       </c>
       <c r="O92" t="n">
-        <v>1385850.046287961</v>
+        <v>1385661.290139051</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5655172414</v>
+        <v>1592.5654664342</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.8758620724</v>
+        <v>264365.8674280772</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.9242252747</v>
+        <v>1630.9242345815</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.807274709</v>
+        <v>1037267.813193834</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1943922358</v>
+        <v>1550.19440684</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4710214234</v>
+        <v>35654.47135732</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>72</v>
       </c>
       <c r="N111" t="n">
-        <v>1579.3858102767</v>
+        <v>1579.3856972112</v>
       </c>
       <c r="O111" t="n">
-        <v>113715.7783399224</v>
+        <v>113715.7701992064</v>
       </c>
       <c r="P111" t="n">
         <v>2900</v>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5364,19 +5364,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="N113" t="n">
         <v>2069.4655178908</v>
       </c>
       <c r="O113" t="n">
-        <v>103473.27589454</v>
+        <v>43458.7758757068</v>
       </c>
       <c r="P113" t="n">
         <v>6500</v>
       </c>
       <c r="Q113" t="n">
-        <v>325000</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="114">
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387544268</v>
+        <v>1516.0387516479</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3924435937</v>
+        <v>836853.3909096408</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -8932,10 +8932,10 @@
         <v>216</v>
       </c>
       <c r="N193" t="n">
-        <v>2079.3834145441</v>
+        <v>2079.3834072432</v>
       </c>
       <c r="O193" t="n">
-        <v>449146.8175415256</v>
+        <v>449146.8159645312</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0163011152</v>
+        <v>1803.0163058036</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.3360966432</v>
+        <v>479602.3373437576</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9024,10 +9024,10 @@
         <v>36</v>
       </c>
       <c r="N195" t="n">
-        <v>3306.5944700461</v>
+        <v>3306.5944615385</v>
       </c>
       <c r="O195" t="n">
-        <v>119037.4009216596</v>
+        <v>119037.400615386</v>
       </c>
       <c r="P195" t="n">
         <v>4900</v>
@@ -9254,10 +9254,10 @@
         <v>233</v>
       </c>
       <c r="N200" t="n">
-        <v>1655.9297327394</v>
+        <v>1655.9297098214</v>
       </c>
       <c r="O200" t="n">
-        <v>385831.6277282802</v>
+        <v>385831.6223883862</v>
       </c>
       <c r="P200" t="n">
         <v>2500</v>
@@ -10830,7 +10830,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -10839,19 +10839,19 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="N234" t="n">
         <v>11332.1</v>
       </c>
       <c r="O234" t="n">
-        <v>487280.3</v>
+        <v>351295.1</v>
       </c>
       <c r="P234" t="n">
         <v>14000</v>
       </c>
       <c r="Q234" t="n">
-        <v>602000</v>
+        <v>434000</v>
       </c>
     </row>
     <row r="235">
@@ -10989,10 +10989,10 @@
         <v>378</v>
       </c>
       <c r="N237" t="n">
-        <v>3110.8390217391</v>
+        <v>3110.8380493577</v>
       </c>
       <c r="O237" t="n">
-        <v>1175897.15021738</v>
+        <v>1175896.782657211</v>
       </c>
       <c r="P237" t="n">
         <v>4500</v>
@@ -11217,10 +11217,10 @@
         <v>11930</v>
       </c>
       <c r="N242" t="n">
-        <v>703.86725350482</v>
+        <v>703.79482873668</v>
       </c>
       <c r="O242" t="n">
-        <v>8397136.334312502</v>
+        <v>8396272.306828592</v>
       </c>
       <c r="P242" t="n">
         <v>900</v>
@@ -14131,7 +14131,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -14140,19 +14140,19 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N303" t="n">
         <v>27577.72</v>
       </c>
       <c r="O303" t="n">
-        <v>303354.92</v>
+        <v>248199.48</v>
       </c>
       <c r="P303" t="n">
         <v>120900</v>
       </c>
       <c r="Q303" t="n">
-        <v>1329900</v>
+        <v>1088100</v>
       </c>
     </row>
     <row r="304">
@@ -15927,10 +15927,10 @@
         <v>50</v>
       </c>
       <c r="N340" t="n">
-        <v>8975.6103797468</v>
+        <v>8919.16</v>
       </c>
       <c r="O340" t="n">
-        <v>448780.51898734</v>
+        <v>445958</v>
       </c>
       <c r="P340" t="n">
         <v>10000</v>
@@ -16699,10 +16699,10 @@
         <v>8</v>
       </c>
       <c r="N356" t="n">
-        <v>7046.939827363</v>
+        <v>7046.9398272138</v>
       </c>
       <c r="O356" t="n">
-        <v>56375.518618904</v>
+        <v>56375.5186177104</v>
       </c>
       <c r="P356" t="n">
         <v>9900</v>
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="J415" t="n">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="K415" t="n">
         <v>0</v>
@@ -19462,19 +19462,19 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="N415" t="n">
         <v>9240</v>
       </c>
       <c r="O415" t="n">
-        <v>5969040</v>
+        <v>5876640</v>
       </c>
       <c r="P415" t="n">
         <v>11500</v>
       </c>
       <c r="Q415" t="n">
-        <v>7429000</v>
+        <v>7314000</v>
       </c>
     </row>
     <row r="416">
@@ -21374,10 +21374,10 @@
         <v>561</v>
       </c>
       <c r="N456" t="n">
-        <v>4687.9746311858</v>
+        <v>4687.974657277</v>
       </c>
       <c r="O456" t="n">
-        <v>2629953.768095233</v>
+        <v>2629953.782732397</v>
       </c>
       <c r="P456" t="n">
         <v>5500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.194960892</v>
+        <v>2360181.189528259</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -4957,10 +4957,10 @@
         <v>11</v>
       </c>
       <c r="N104" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O104" t="n">
-        <v>131135.4</v>
+        <v>131447.379540048</v>
       </c>
       <c r="P104" t="n">
         <v>19900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.813193834</v>
+        <v>1037267.817650286</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5978,10 +5978,10 @@
         <v>103</v>
       </c>
       <c r="N127" t="n">
-        <v>5449.5305454545</v>
+        <v>5449.5305504587</v>
       </c>
       <c r="O127" t="n">
-        <v>561301.6461818134</v>
+        <v>561301.6466972461</v>
       </c>
       <c r="P127" t="n">
         <v>6200</v>
@@ -7540,10 +7540,10 @@
         <v>35</v>
       </c>
       <c r="N163" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O163" t="n">
-        <v>182635.9703434595</v>
+        <v>182635.9703973525</v>
       </c>
       <c r="P163" t="n">
         <v>8500</v>
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3909096408</v>
+        <v>836853.3907698744</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -11217,10 +11217,10 @@
         <v>11930</v>
       </c>
       <c r="N242" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O242" t="n">
-        <v>8396272.306828592</v>
+        <v>8396272.297290558</v>
       </c>
       <c r="P242" t="n">
         <v>900</v>
@@ -17137,10 +17137,10 @@
         <v>11</v>
       </c>
       <c r="N365" t="n">
-        <v>366.39971428571</v>
+        <v>366.39971014493</v>
       </c>
       <c r="O365" t="n">
-        <v>4030.39685714281</v>
+        <v>4030.39681159423</v>
       </c>
       <c r="P365" t="n">
         <v>2900</v>
@@ -18959,10 +18959,10 @@
         <v>63</v>
       </c>
       <c r="N404" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O404" t="n">
-        <v>123017.58</v>
+        <v>125436.465</v>
       </c>
       <c r="P404" t="n">
         <v>3500</v>
@@ -20533,10 +20533,10 @@
         <v>3</v>
       </c>
       <c r="N438" t="n">
-        <v>751.45</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="O438" t="n">
-        <v>2254.35</v>
+        <v>3279.0545454546</v>
       </c>
       <c r="P438" t="n">
         <v>2500</v>
@@ -21420,10 +21420,10 @@
         <v>80</v>
       </c>
       <c r="N457" t="n">
-        <v>4171.6685988024</v>
+        <v>4171.6685954382</v>
       </c>
       <c r="O457" t="n">
-        <v>333733.487904192</v>
+        <v>333733.487635056</v>
       </c>
       <c r="P457" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q531"/>
+  <dimension ref="A1:Q530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.3101659125</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2354586455</v>
+        <v>162931.2354751125</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2551307749</v>
+        <v>2582.2550693069</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.189528259</v>
+        <v>2360181.133346507</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.895979825</v>
+        <v>5216.8959750483</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.364723399</v>
+        <v>7053243.358265301</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2532489451</v>
+        <v>3594.2532155477</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.0849788907</v>
+        <v>923723.0763957589</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712622683</v>
+        <v>4371.1712623543</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.290139051</v>
+        <v>1385661.290166313</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5654664342</v>
+        <v>1592.5654585153</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.8674280772</v>
+        <v>264365.8661135398</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -4957,10 +4957,10 @@
         <v>11</v>
       </c>
       <c r="N104" t="n">
-        <v>11949.761776368</v>
+        <v>11921.4</v>
       </c>
       <c r="O104" t="n">
-        <v>131447.379540048</v>
+        <v>131135.4</v>
       </c>
       <c r="P104" t="n">
         <v>19900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.9242415885</v>
+        <v>1630.9242710358</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.817650286</v>
+        <v>1037267.836378769</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.19440684</v>
+        <v>1550.1944427152</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.47135732</v>
+        <v>35654.4721824496</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>72</v>
       </c>
       <c r="N111" t="n">
-        <v>1579.3856972112</v>
+        <v>1579.38564</v>
       </c>
       <c r="O111" t="n">
-        <v>113715.7701992064</v>
+        <v>113715.76608</v>
       </c>
       <c r="P111" t="n">
         <v>2900</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>2029.8740827436</v>
+        <v>2029.8740849673</v>
       </c>
       <c r="O129" t="n">
-        <v>4059.7481654872</v>
+        <v>4059.7481699346</v>
       </c>
       <c r="P129" t="n">
         <v>3600</v>
@@ -6826,10 +6826,10 @@
         <v>21</v>
       </c>
       <c r="N147" t="n">
-        <v>1508.5869767442</v>
+        <v>1508.5869047619</v>
       </c>
       <c r="O147" t="n">
-        <v>31680.3265116282</v>
+        <v>31680.3249999999</v>
       </c>
       <c r="P147" t="n">
         <v>3600</v>
@@ -8840,10 +8840,10 @@
         <v>312</v>
       </c>
       <c r="N191" t="n">
-        <v>2458.5126365879</v>
+        <v>2458.5126313933</v>
       </c>
       <c r="O191" t="n">
-        <v>767055.9426154249</v>
+        <v>767055.9409947096</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -8932,10 +8932,10 @@
         <v>216</v>
       </c>
       <c r="N193" t="n">
-        <v>2079.3834072432</v>
+        <v>2079.3833876946</v>
       </c>
       <c r="O193" t="n">
-        <v>449146.8159645312</v>
+        <v>449146.8117420336</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0163058036</v>
+        <v>1803.0164892802</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.3373437576</v>
+        <v>479602.3861485332</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>72</v>
       </c>
       <c r="N197" t="n">
-        <v>2108.7956032172</v>
+        <v>2108.7956591928</v>
       </c>
       <c r="O197" t="n">
-        <v>151833.2834316384</v>
+        <v>151833.2874618816</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9162,10 +9162,10 @@
         <v>192</v>
       </c>
       <c r="N198" t="n">
-        <v>2056.0823271375</v>
+        <v>2056.0823128492</v>
       </c>
       <c r="O198" t="n">
-        <v>394767.8068104</v>
+        <v>394767.8040670464</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9208,10 +9208,10 @@
         <v>162</v>
       </c>
       <c r="N199" t="n">
-        <v>3224.5693668237</v>
+        <v>3224.5693815514</v>
       </c>
       <c r="O199" t="n">
-        <v>522380.2374254394</v>
+        <v>522380.2398113268</v>
       </c>
       <c r="P199" t="n">
         <v>4500</v>
@@ -9390,10 +9390,10 @@
         <v>2</v>
       </c>
       <c r="N203" t="n">
-        <v>1906.1788059701</v>
+        <v>1906.178</v>
       </c>
       <c r="O203" t="n">
-        <v>3812.3576119402</v>
+        <v>3812.356</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -10505,10 +10505,10 @@
         <v>1</v>
       </c>
       <c r="N227" t="n">
-        <v>1690.870009298</v>
+        <v>1690.8700093371</v>
       </c>
       <c r="O227" t="n">
-        <v>1690.870009298</v>
+        <v>1690.8700093371</v>
       </c>
       <c r="P227" t="n">
         <v>3000</v>
@@ -10989,10 +10989,10 @@
         <v>378</v>
       </c>
       <c r="N237" t="n">
-        <v>3110.8380493577</v>
+        <v>3110.8379516019</v>
       </c>
       <c r="O237" t="n">
-        <v>1175896.782657211</v>
+        <v>1175896.745705518</v>
       </c>
       <c r="P237" t="n">
         <v>4500</v>
@@ -11217,10 +11217,10 @@
         <v>11930</v>
       </c>
       <c r="N242" t="n">
-        <v>703.79482793718</v>
+        <v>703.79482106458</v>
       </c>
       <c r="O242" t="n">
-        <v>8396272.297290558</v>
+        <v>8396272.215300439</v>
       </c>
       <c r="P242" t="n">
         <v>900</v>
@@ -14290,10 +14290,10 @@
         <v>60</v>
       </c>
       <c r="N306" t="n">
-        <v>3067.0906122449</v>
+        <v>3067.0906143345</v>
       </c>
       <c r="O306" t="n">
-        <v>184025.436734694</v>
+        <v>184025.43686007</v>
       </c>
       <c r="P306" t="n">
         <v>7200</v>
@@ -14870,10 +14870,10 @@
         <v>1000</v>
       </c>
       <c r="N318" t="n">
-        <v>1783.7988756856</v>
+        <v>1783.7988736264</v>
       </c>
       <c r="O318" t="n">
-        <v>1783798.8756856</v>
+        <v>1783798.8736264</v>
       </c>
       <c r="P318" t="n">
         <v>1500</v>
@@ -17480,10 +17480,10 @@
         <v>726</v>
       </c>
       <c r="N372" t="n">
-        <v>465.8709683605</v>
+        <v>465.8709970385</v>
       </c>
       <c r="O372" t="n">
-        <v>338222.323029723</v>
+        <v>338222.343849951</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -18340,12 +18340,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>DPBQ05</t>
+          <t>DPBQ09</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>PELUCHE ABRASADO WZ44</t>
+          <t>PELUCHE PATRULLA PQÑ 20CM PATROL</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -18359,7 +18359,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -18368,30 +18368,30 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="N391" t="n">
-        <v>4518.3764150943</v>
+        <v>5384.62</v>
       </c>
       <c r="O391" t="n">
-        <v>230437.1971698093</v>
+        <v>5384.62</v>
       </c>
       <c r="P391" t="n">
-        <v>11500</v>
+        <v>7000</v>
       </c>
       <c r="Q391" t="n">
-        <v>586500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>DPBQ09</t>
+          <t>DPBQ11</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>PELUCHE PATRULLA PQÑ 20CM PATROL</t>
+          <t>PELUCHE PERRO STD 25CM  PERROX3</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -18417,27 +18417,27 @@
         <v>1</v>
       </c>
       <c r="N392" t="n">
-        <v>5384.62</v>
+        <v>9153.85</v>
       </c>
       <c r="O392" t="n">
-        <v>5384.62</v>
+        <v>9153.85</v>
       </c>
       <c r="P392" t="n">
-        <v>7000</v>
+        <v>11900</v>
       </c>
       <c r="Q392" t="n">
-        <v>7000</v>
+        <v>11900</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>DPBQ11</t>
+          <t>DPBQ15</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO STD 25CM  PERROX3</t>
+          <t>PELUCHE TIGRES 25CM</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -18463,27 +18463,27 @@
         <v>1</v>
       </c>
       <c r="N393" t="n">
-        <v>9153.85</v>
+        <v>7280.46</v>
       </c>
       <c r="O393" t="n">
-        <v>9153.85</v>
+        <v>7280.46</v>
       </c>
       <c r="P393" t="n">
-        <v>11900</v>
+        <v>16900</v>
       </c>
       <c r="Q393" t="n">
-        <v>11900</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>DPBQ15</t>
+          <t>DPBQ16</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRES 25CM</t>
+          <t>PELUCHE PERRO SENTADO 28CM</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
@@ -18506,30 +18506,30 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N394" t="n">
-        <v>7280.46</v>
+        <v>5782.36</v>
       </c>
       <c r="O394" t="n">
-        <v>7280.46</v>
+        <v>17347.08</v>
       </c>
       <c r="P394" t="n">
-        <v>16900</v>
+        <v>15900</v>
       </c>
       <c r="Q394" t="n">
-        <v>16900</v>
+        <v>47700</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>DPBQ16</t>
+          <t>DPBQ18</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 28CM</t>
+          <t>PELUCHE VIEJITOS 25CM</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -18552,30 +18552,30 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N395" t="n">
-        <v>5782.36</v>
+        <v>2868.67</v>
       </c>
       <c r="O395" t="n">
-        <v>17347.08</v>
+        <v>31555.37</v>
       </c>
       <c r="P395" t="n">
-        <v>15900</v>
+        <v>16900</v>
       </c>
       <c r="Q395" t="n">
-        <v>47700</v>
+        <v>185900</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>DPBQ18</t>
+          <t>DPBQ26</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>PELUCHE VIEJITOS 25CM</t>
+          <t>PELUCHE OSO CUMPLEAÑOS 30CM</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
@@ -18598,35 +18598,35 @@
         <v>0</v>
       </c>
       <c r="M396" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N396" t="n">
-        <v>2868.67</v>
+        <v>2223.11</v>
       </c>
       <c r="O396" t="n">
-        <v>31555.37</v>
+        <v>11115.55</v>
       </c>
       <c r="P396" t="n">
-        <v>16900</v>
+        <v>25000</v>
       </c>
       <c r="Q396" t="n">
-        <v>185900</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>DPBQ26</t>
+          <t>DV052</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>PELUCHE OSO CUMPLEAÑOS 30CM</t>
+          <t>PELOTA PISCINA DV052</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>5</v>
+        <v>1527</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -18644,30 +18644,30 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>5</v>
+        <v>1527</v>
       </c>
       <c r="N397" t="n">
-        <v>2223.11</v>
+        <v>220.00227919632</v>
       </c>
       <c r="O397" t="n">
-        <v>11115.55</v>
+        <v>335943.4803327806</v>
       </c>
       <c r="P397" t="n">
-        <v>25000</v>
+        <v>260</v>
       </c>
       <c r="Q397" t="n">
-        <v>125000</v>
+        <v>397020</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>DV052</t>
+          <t>DV077</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA DV052</t>
+          <t>RELLENO DE PIÑATA GDE DV077</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>1527</v>
+        <v>20</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
@@ -18690,30 +18690,30 @@
         <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>1527</v>
+        <v>20</v>
       </c>
       <c r="N398" t="n">
-        <v>220.00227919632</v>
+        <v>705.11</v>
       </c>
       <c r="O398" t="n">
-        <v>335943.4803327806</v>
+        <v>14102.2</v>
       </c>
       <c r="P398" t="n">
-        <v>260</v>
+        <v>11000</v>
       </c>
       <c r="Q398" t="n">
-        <v>397020</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>DV077</t>
+          <t>DV083</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>RELLENO DE PIÑATA GDE DV077</t>
+          <t>RELLENO PIÑATA PQÑ DV083</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -18727,7 +18727,7 @@
         </is>
       </c>
       <c r="J399" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K399" t="n">
         <v>0</v>
@@ -18736,30 +18736,30 @@
         <v>0</v>
       </c>
       <c r="M399" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N399" t="n">
-        <v>705.11</v>
+        <v>504.3</v>
       </c>
       <c r="O399" t="n">
-        <v>14102.2</v>
+        <v>3530.1</v>
       </c>
       <c r="P399" t="n">
-        <v>11000</v>
+        <v>5900</v>
       </c>
       <c r="Q399" t="n">
-        <v>220000</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>DV083</t>
+          <t>EMI066</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>RELLENO PIÑATA PQÑ DV083</t>
+          <t>PELUCHE ENCANTO E22-11</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K400" t="n">
         <v>0</v>
@@ -18782,35 +18782,35 @@
         <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N400" t="n">
-        <v>504.3</v>
+        <v>11475</v>
       </c>
       <c r="O400" t="n">
-        <v>3530.1</v>
+        <v>34425</v>
       </c>
       <c r="P400" t="n">
-        <v>5900</v>
+        <v>14900</v>
       </c>
       <c r="Q400" t="n">
-        <v>41300</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>EMI066</t>
+          <t>FG045</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>PELUCHE ENCANTO E22-11</t>
+          <t>HELICPTERO DIDACTICO BOLSA BP1235513</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -18819,7 +18819,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -18828,44 +18828,34 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="N401" t="n">
-        <v>11475</v>
+        <v>5120.05</v>
       </c>
       <c r="O401" t="n">
-        <v>34425</v>
+        <v>240642.35</v>
       </c>
       <c r="P401" t="n">
-        <v>14900</v>
+        <v>5700</v>
       </c>
       <c r="Q401" t="n">
-        <v>44700</v>
+        <v>267900</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>FG045</t>
+          <t>FG046</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>HELICPTERO DIDACTICO BOLSA BP1235513</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>CARRO DINOSAURIO JD1899-108A</t>
         </is>
       </c>
       <c r="J402" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -18874,34 +18864,44 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="N402" t="n">
-        <v>5120.05</v>
+        <v>3885.95</v>
       </c>
       <c r="O402" t="n">
-        <v>240642.35</v>
+        <v>3885.95</v>
       </c>
       <c r="P402" t="n">
-        <v>5700</v>
+        <v>6700</v>
       </c>
       <c r="Q402" t="n">
-        <v>267900</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>FG046</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO JD1899-108A</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J403" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
@@ -18910,35 +18910,35 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="N403" t="n">
-        <v>3885.95</v>
+        <v>1952.66</v>
       </c>
       <c r="O403" t="n">
-        <v>3885.95</v>
+        <v>123017.58</v>
       </c>
       <c r="P403" t="n">
-        <v>6700</v>
+        <v>3500</v>
       </c>
       <c r="Q403" t="n">
-        <v>6700</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG055</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>FICHAS DIDACTICAS CARRITO 2263</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
@@ -18956,35 +18956,35 @@
         <v>0</v>
       </c>
       <c r="M404" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="N404" t="n">
-        <v>1991.055</v>
+        <v>12575.25</v>
       </c>
       <c r="O404" t="n">
-        <v>125436.465</v>
+        <v>301806</v>
       </c>
       <c r="P404" t="n">
-        <v>3500</v>
+        <v>17900</v>
       </c>
       <c r="Q404" t="n">
-        <v>220500</v>
+        <v>429600</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>FG055</t>
+          <t>FG067</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>FICHAS DIDACTICAS CARRITO 2263</t>
+          <t>COCINA BOLSA 7003-1</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -19002,30 +19002,30 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N405" t="n">
-        <v>12575.25</v>
+        <v>6270.21</v>
       </c>
       <c r="O405" t="n">
-        <v>301806</v>
+        <v>125404.2</v>
       </c>
       <c r="P405" t="n">
-        <v>17900</v>
+        <v>8900</v>
       </c>
       <c r="Q405" t="n">
-        <v>429600</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>FG067</t>
+          <t>FG08</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>COCINA BOLSA 7003-1</t>
+          <t>JUEGO DOCTOR MALETA NIÑO 118-88A</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -19039,7 +19039,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -19048,35 +19048,35 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N406" t="n">
-        <v>6270.21</v>
+        <v>7625.7242857143</v>
       </c>
       <c r="O406" t="n">
-        <v>125404.2</v>
+        <v>76257.24285714301</v>
       </c>
       <c r="P406" t="n">
-        <v>8900</v>
+        <v>29900</v>
       </c>
       <c r="Q406" t="n">
-        <v>178000</v>
+        <v>299000</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>FG08</t>
+          <t>FG081</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>JUEGO DOCTOR MALETA NIÑO 118-88A</t>
+          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="J407" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K407" t="n">
         <v>0</v>
@@ -19094,35 +19094,35 @@
         <v>0</v>
       </c>
       <c r="M407" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N407" t="n">
-        <v>7625.7242857143</v>
+        <v>9726.98</v>
       </c>
       <c r="O407" t="n">
-        <v>76257.24285714301</v>
+        <v>175085.64</v>
       </c>
       <c r="P407" t="n">
-        <v>29900</v>
+        <v>12900</v>
       </c>
       <c r="Q407" t="n">
-        <v>299000</v>
+        <v>232200</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>FG081</t>
+          <t>FG084</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
+          <t>BEBE BAÑERA 9431FH7</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="J408" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K408" t="n">
         <v>0</v>
@@ -19140,35 +19140,35 @@
         <v>0</v>
       </c>
       <c r="M408" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N408" t="n">
-        <v>9726.98</v>
+        <v>9398.26</v>
       </c>
       <c r="O408" t="n">
-        <v>175085.64</v>
+        <v>9398.26</v>
       </c>
       <c r="P408" t="n">
-        <v>12900</v>
+        <v>9900</v>
       </c>
       <c r="Q408" t="n">
-        <v>232200</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>FG084</t>
+          <t>FG089</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>BEBE BAÑERA 9431FH7</t>
+          <t>MULA EN BOLSA CON CARROS 919-113</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="J409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K409" t="n">
         <v>0</v>
@@ -19186,35 +19186,35 @@
         <v>0</v>
       </c>
       <c r="M409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N409" t="n">
-        <v>9398.26</v>
+        <v>13958.03</v>
       </c>
       <c r="O409" t="n">
-        <v>9398.26</v>
+        <v>27916.06</v>
       </c>
       <c r="P409" t="n">
-        <v>9900</v>
+        <v>14900</v>
       </c>
       <c r="Q409" t="n">
-        <v>9900</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>FG089</t>
+          <t>FG092</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>MULA EN BOLSA CON CARROS 919-113</t>
+          <t>BLISTER  TETERA SJ377-1</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -19223,7 +19223,7 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
@@ -19232,35 +19232,35 @@
         <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N410" t="n">
-        <v>13958.03</v>
+        <v>9855.0380769231</v>
       </c>
       <c r="O410" t="n">
-        <v>27916.06</v>
+        <v>29565.1142307693</v>
       </c>
       <c r="P410" t="n">
-        <v>14900</v>
+        <v>15500</v>
       </c>
       <c r="Q410" t="n">
-        <v>29800</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>FG092</t>
+          <t>FP-315-ELEFANTE</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BLISTER  TETERA SJ377-1</t>
+          <t>PELUCHE ELEFANTE  48CM</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -19269,7 +19269,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -19278,35 +19278,35 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N411" t="n">
-        <v>9855.0380769231</v>
+        <v>29250</v>
       </c>
       <c r="O411" t="n">
-        <v>29565.1142307693</v>
+        <v>29250</v>
       </c>
       <c r="P411" t="n">
-        <v>15500</v>
+        <v>36900</v>
       </c>
       <c r="Q411" t="n">
-        <v>46500</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>FP-315-ELEFANTE</t>
+          <t>FP-339</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>PELUCHE ELEFANTE  48CM</t>
+          <t>PELUCHE CIGUEÑA CON HUEVITOS 25CM FP-339</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -19324,30 +19324,30 @@
         <v>0</v>
       </c>
       <c r="M412" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N412" t="n">
-        <v>29250</v>
+        <v>21150</v>
       </c>
       <c r="O412" t="n">
-        <v>29250</v>
+        <v>63450</v>
       </c>
       <c r="P412" t="n">
-        <v>36900</v>
+        <v>26500</v>
       </c>
       <c r="Q412" t="n">
-        <v>36900</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>FP-339</t>
+          <t>J-138</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>PELUCHE CIGUEÑA CON HUEVITOS 25CM FP-339</t>
+          <t>PERRO CAMINA J-138</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="J413" t="n">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="K413" t="n">
         <v>0</v>
@@ -19370,30 +19370,30 @@
         <v>0</v>
       </c>
       <c r="M413" t="n">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="N413" t="n">
-        <v>21150</v>
+        <v>6160</v>
       </c>
       <c r="O413" t="n">
-        <v>63450</v>
+        <v>1774080</v>
       </c>
       <c r="P413" t="n">
-        <v>26500</v>
+        <v>7500</v>
       </c>
       <c r="Q413" t="n">
-        <v>79500</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>J-138</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PERRO CAMINA J-138</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>288</v>
+        <v>636</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
@@ -19416,30 +19416,30 @@
         <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>288</v>
+        <v>636</v>
       </c>
       <c r="N414" t="n">
-        <v>6160</v>
+        <v>9240</v>
       </c>
       <c r="O414" t="n">
-        <v>1774080</v>
+        <v>5876640</v>
       </c>
       <c r="P414" t="n">
-        <v>7500</v>
+        <v>11500</v>
       </c>
       <c r="Q414" t="n">
-        <v>2160000</v>
+        <v>7314000</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>J-582</t>
+          <t>LP089</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>SET DE BICHOS EN BOLSA 714K-1</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="J415" t="n">
-        <v>636</v>
+        <v>25</v>
       </c>
       <c r="K415" t="n">
         <v>0</v>
@@ -19462,30 +19462,30 @@
         <v>0</v>
       </c>
       <c r="M415" t="n">
-        <v>636</v>
+        <v>25</v>
       </c>
       <c r="N415" t="n">
-        <v>9240</v>
+        <v>10320</v>
       </c>
       <c r="O415" t="n">
-        <v>5876640</v>
+        <v>258000</v>
       </c>
       <c r="P415" t="n">
-        <v>11500</v>
+        <v>12900</v>
       </c>
       <c r="Q415" t="n">
-        <v>7314000</v>
+        <v>322500</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>LP089</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SET DE BICHOS EN BOLSA 714K-1</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="J416" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K416" t="n">
         <v>0</v>
@@ -19508,35 +19508,35 @@
         <v>0</v>
       </c>
       <c r="M416" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N416" t="n">
-        <v>10320</v>
+        <v>415.07</v>
       </c>
       <c r="O416" t="n">
-        <v>258000</v>
+        <v>5395.91</v>
       </c>
       <c r="P416" t="n">
-        <v>12900</v>
+        <v>2900</v>
       </c>
       <c r="Q416" t="n">
-        <v>322500</v>
+        <v>37700</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>MFQ01</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>PELUCHE ERIZO 55CM 23FP-029</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -19545,7 +19545,7 @@
         </is>
       </c>
       <c r="J417" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K417" t="n">
         <v>0</v>
@@ -19554,44 +19554,34 @@
         <v>0</v>
       </c>
       <c r="M417" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N417" t="n">
-        <v>415.07</v>
+        <v>17885.0975</v>
       </c>
       <c r="O417" t="n">
-        <v>5395.91</v>
+        <v>71540.39</v>
       </c>
       <c r="P417" t="n">
-        <v>2900</v>
+        <v>46500</v>
       </c>
       <c r="Q417" t="n">
-        <v>37700</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MFQ01</t>
+          <t>MFQ11</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>PELUCHE ERIZO 55CM 23FP-029</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
         </is>
       </c>
       <c r="J418" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K418" t="n">
         <v>0</v>
@@ -19600,34 +19590,34 @@
         <v>0</v>
       </c>
       <c r="M418" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N418" t="n">
-        <v>17885.0975</v>
+        <v>10436.368888889</v>
       </c>
       <c r="O418" t="n">
-        <v>71540.39</v>
+        <v>93927.320000001</v>
       </c>
       <c r="P418" t="n">
-        <v>46500</v>
+        <v>25900</v>
       </c>
       <c r="Q418" t="n">
-        <v>186000</v>
+        <v>233100</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>MFQ11</t>
+          <t>MFQ12</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK 30CM FP-165</t>
+          <t>PELUCHE DINOSAURIO PK FP-166</t>
         </is>
       </c>
       <c r="J419" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K419" t="n">
         <v>0</v>
@@ -19636,34 +19626,49 @@
         <v>0</v>
       </c>
       <c r="M419" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>10436.368888889</v>
+        <v>8736.825000000001</v>
       </c>
       <c r="O419" t="n">
-        <v>93927.320000001</v>
+        <v>17473.65</v>
       </c>
       <c r="P419" t="n">
-        <v>25900</v>
+        <v>26500</v>
       </c>
       <c r="Q419" t="n">
-        <v>233100</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>MFQ12</t>
+          <t>MG033</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>MG18880</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO PK FP-166</t>
+          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J420" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -19672,40 +19677,40 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N420" t="n">
-        <v>8736.825000000001</v>
+        <v>1783.57</v>
       </c>
       <c r="O420" t="n">
-        <v>17473.65</v>
+        <v>21402.84</v>
       </c>
       <c r="P420" t="n">
-        <v>26500</v>
+        <v>7800</v>
       </c>
       <c r="Q420" t="n">
-        <v>53000</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>MG033</t>
+          <t>MG045</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>MG18880</t>
+          <t>PT20032</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SET VAJILLA METALIZADA MG18880/MG033</t>
+          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -19714,7 +19719,7 @@
         </is>
       </c>
       <c r="J421" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K421" t="n">
         <v>0</v>
@@ -19723,40 +19728,35 @@
         <v>0</v>
       </c>
       <c r="M421" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N421" t="n">
-        <v>1783.57</v>
+        <v>6000</v>
       </c>
       <c r="O421" t="n">
-        <v>21402.84</v>
+        <v>210000</v>
       </c>
       <c r="P421" t="n">
-        <v>7800</v>
+        <v>7500</v>
       </c>
       <c r="Q421" t="n">
-        <v>93600</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>MG045</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>PT20032</t>
+          <t>MG090</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>MARIMBA ANIMALES MADERA PQÑ PT20032</t>
+          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -19765,7 +19765,7 @@
         </is>
       </c>
       <c r="J422" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K422" t="n">
         <v>0</v>
@@ -19774,35 +19774,40 @@
         <v>0</v>
       </c>
       <c r="M422" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="N422" t="n">
-        <v>6000</v>
+        <v>1462.04</v>
       </c>
       <c r="O422" t="n">
-        <v>210000</v>
+        <v>4386.12</v>
       </c>
       <c r="P422" t="n">
-        <v>7500</v>
+        <v>3800</v>
       </c>
       <c r="Q422" t="n">
-        <v>262500</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MG090</t>
+          <t>MG093</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>mg26016</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>TELEFONO CUERDA PQÑ MG18986/MG090</t>
+          <t>CARRO BASURA BOLSA MG26016</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -19811,7 +19816,7 @@
         </is>
       </c>
       <c r="J423" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="K423" t="n">
         <v>0</v>
@@ -19820,40 +19825,35 @@
         <v>0</v>
       </c>
       <c r="M423" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="N423" t="n">
-        <v>1462.04</v>
+        <v>770.6799999999999</v>
       </c>
       <c r="O423" t="n">
-        <v>4386.12</v>
+        <v>22349.72</v>
       </c>
       <c r="P423" t="n">
-        <v>3800</v>
+        <v>17800</v>
       </c>
       <c r="Q423" t="n">
-        <v>11400</v>
+        <v>516200</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>MG093</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>mg26016</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>CARRO BASURA BOLSA MG26016</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -19862,7 +19862,7 @@
         </is>
       </c>
       <c r="J424" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K424" t="n">
         <v>0</v>
@@ -19871,35 +19871,35 @@
         <v>0</v>
       </c>
       <c r="M424" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N424" t="n">
-        <v>770.6799999999999</v>
+        <v>1482.84</v>
       </c>
       <c r="O424" t="n">
-        <v>22349.72</v>
+        <v>40036.68</v>
       </c>
       <c r="P424" t="n">
-        <v>17800</v>
+        <v>6500</v>
       </c>
       <c r="Q424" t="n">
-        <v>516200</v>
+        <v>175500</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
@@ -19917,35 +19917,35 @@
         <v>0</v>
       </c>
       <c r="M425" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="N425" t="n">
-        <v>1482.84</v>
+        <v>576.58</v>
       </c>
       <c r="O425" t="n">
-        <v>40036.68</v>
+        <v>33441.64</v>
       </c>
       <c r="P425" t="n">
-        <v>6500</v>
+        <v>5900</v>
       </c>
       <c r="Q425" t="n">
-        <v>175500</v>
+        <v>342200</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -19954,7 +19954,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -19963,35 +19963,40 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N426" t="n">
-        <v>576.58</v>
+        <v>1129.14</v>
       </c>
       <c r="O426" t="n">
-        <v>33441.64</v>
+        <v>68877.54000000001</v>
       </c>
       <c r="P426" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q426" t="n">
-        <v>342200</v>
+        <v>420900</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -20000,7 +20005,7 @@
         </is>
       </c>
       <c r="J427" t="n">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="K427" t="n">
         <v>0</v>
@@ -20009,40 +20014,35 @@
         <v>0</v>
       </c>
       <c r="M427" t="n">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="N427" t="n">
-        <v>1129.14</v>
+        <v>1236.3</v>
       </c>
       <c r="O427" t="n">
-        <v>68877.54000000001</v>
+        <v>279403.8</v>
       </c>
       <c r="P427" t="n">
-        <v>6900</v>
+        <v>2300</v>
       </c>
       <c r="Q427" t="n">
-        <v>420900</v>
+        <v>519800</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="J428" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="K428" t="n">
         <v>0</v>
@@ -20060,35 +20060,35 @@
         <v>0</v>
       </c>
       <c r="M428" t="n">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="N428" t="n">
-        <v>1236.3</v>
+        <v>8174.05</v>
       </c>
       <c r="O428" t="n">
-        <v>279403.8</v>
+        <v>16348.1</v>
       </c>
       <c r="P428" t="n">
-        <v>2300</v>
+        <v>8900</v>
       </c>
       <c r="Q428" t="n">
-        <v>519800</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -20106,35 +20106,35 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N429" t="n">
-        <v>8174.05</v>
+        <v>11433.53</v>
       </c>
       <c r="O429" t="n">
-        <v>16348.1</v>
+        <v>45734.12</v>
       </c>
       <c r="P429" t="n">
-        <v>8900</v>
+        <v>15000</v>
       </c>
       <c r="Q429" t="n">
-        <v>17800</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG26011</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>CAMION DE BOMBEROS MG26011</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -20143,7 +20143,7 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
@@ -20152,30 +20152,30 @@
         <v>0</v>
       </c>
       <c r="M430" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N430" t="n">
-        <v>11433.53</v>
+        <v>5920.69</v>
       </c>
       <c r="O430" t="n">
-        <v>45734.12</v>
+        <v>29603.45</v>
       </c>
       <c r="P430" t="n">
-        <v>15000</v>
+        <v>11900</v>
       </c>
       <c r="Q430" t="n">
-        <v>60000</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>MG26011</t>
+          <t>MG26196</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>CAMION DE BOMBEROS MG26011</t>
+          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -20189,7 +20189,7 @@
         </is>
       </c>
       <c r="J431" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K431" t="n">
         <v>0</v>
@@ -20198,30 +20198,30 @@
         <v>0</v>
       </c>
       <c r="M431" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N431" t="n">
-        <v>5920.69</v>
+        <v>6272.36</v>
       </c>
       <c r="O431" t="n">
-        <v>29603.45</v>
+        <v>94085.39999999999</v>
       </c>
       <c r="P431" t="n">
-        <v>11900</v>
+        <v>10500</v>
       </c>
       <c r="Q431" t="n">
-        <v>59500</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MG26196</t>
+          <t>MG27332</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
+          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -20235,7 +20235,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -20244,30 +20244,30 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N432" t="n">
-        <v>6272.36</v>
+        <v>6750.7</v>
       </c>
       <c r="O432" t="n">
-        <v>94085.39999999999</v>
+        <v>135014</v>
       </c>
       <c r="P432" t="n">
-        <v>10500</v>
+        <v>22500</v>
       </c>
       <c r="Q432" t="n">
-        <v>157500</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>MG27332</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SET DE CARROS DIDACTICOS CONSTRUCCION X4 PCS MG27332</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -20281,7 +20281,7 @@
         </is>
       </c>
       <c r="J433" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K433" t="n">
         <v>0</v>
@@ -20290,35 +20290,35 @@
         <v>0</v>
       </c>
       <c r="M433" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N433" t="n">
-        <v>6750.7</v>
+        <v>9046.99</v>
       </c>
       <c r="O433" t="n">
-        <v>135014</v>
+        <v>63328.93</v>
       </c>
       <c r="P433" t="n">
         <v>22500</v>
       </c>
       <c r="Q433" t="n">
-        <v>450000</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG32315</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="J434" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="K434" t="n">
         <v>0</v>
@@ -20336,35 +20336,40 @@
         <v>0</v>
       </c>
       <c r="M434" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="N434" t="n">
-        <v>9046.99</v>
+        <v>1319.3609287926</v>
       </c>
       <c r="O434" t="n">
-        <v>63328.93</v>
+        <v>50135.7152941188</v>
       </c>
       <c r="P434" t="n">
-        <v>22500</v>
+        <v>3500</v>
       </c>
       <c r="Q434" t="n">
-        <v>157500</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>MG32315</t>
+          <t>MG32342</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>MG32342</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SET MUÑECO ACOSTADO MILITAR BLISTER MG32315</t>
+          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -20373,7 +20378,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -20382,40 +20387,35 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="N435" t="n">
-        <v>1319.3609287926</v>
+        <v>1161.6</v>
       </c>
       <c r="O435" t="n">
-        <v>50135.7152941188</v>
+        <v>20908.8</v>
       </c>
       <c r="P435" t="n">
-        <v>3500</v>
+        <v>24500</v>
       </c>
       <c r="Q435" t="n">
-        <v>133000</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>MG32342</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>MG32342</t>
+          <t>MG32594</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>ROBOT CON MOVIMIENTOS LUZ Y SONIDO MG32342</t>
+          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -20424,7 +20424,7 @@
         </is>
       </c>
       <c r="J436" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="K436" t="n">
         <v>0</v>
@@ -20433,35 +20433,40 @@
         <v>0</v>
       </c>
       <c r="M436" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="N436" t="n">
-        <v>1161.6</v>
+        <v>3088.1452173913</v>
       </c>
       <c r="O436" t="n">
-        <v>20908.8</v>
+        <v>111173.2278260868</v>
       </c>
       <c r="P436" t="n">
-        <v>24500</v>
+        <v>8500</v>
       </c>
       <c r="Q436" t="n">
-        <v>441000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>MG32594</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO X 2EN BOLSA MG32594</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -20470,7 +20475,7 @@
         </is>
       </c>
       <c r="J437" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K437" t="n">
         <v>0</v>
@@ -20479,40 +20484,35 @@
         <v>0</v>
       </c>
       <c r="M437" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="N437" t="n">
-        <v>3088.1452173913</v>
+        <v>751.45</v>
       </c>
       <c r="O437" t="n">
-        <v>111173.2278260868</v>
+        <v>2254.35</v>
       </c>
       <c r="P437" t="n">
-        <v>8500</v>
+        <v>2500</v>
       </c>
       <c r="Q437" t="n">
-        <v>306000</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="J438" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="K438" t="n">
         <v>0</v>
@@ -20530,35 +20530,35 @@
         <v>0</v>
       </c>
       <c r="M438" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
       <c r="N438" t="n">
-        <v>1093.0181818182</v>
+        <v>571.87</v>
       </c>
       <c r="O438" t="n">
-        <v>3279.0545454546</v>
+        <v>86924.24000000001</v>
       </c>
       <c r="P438" t="n">
         <v>2500</v>
       </c>
       <c r="Q438" t="n">
-        <v>7500</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
@@ -20576,30 +20576,35 @@
         <v>0</v>
       </c>
       <c r="M439" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="N439" t="n">
-        <v>571.87</v>
+        <v>310.4175</v>
       </c>
       <c r="O439" t="n">
-        <v>86924.24000000001</v>
+        <v>310.4175</v>
       </c>
       <c r="P439" t="n">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="Q439" t="n">
-        <v>380000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG40243</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>MG40243</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>ATARY DINOSAURIO MG40243</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -20613,7 +20618,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -20622,40 +20627,35 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N440" t="n">
-        <v>310.4175</v>
+        <v>520.674</v>
       </c>
       <c r="O440" t="n">
-        <v>310.4175</v>
+        <v>4165.392</v>
       </c>
       <c r="P440" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="Q440" t="n">
-        <v>1800</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>MG40243</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>MG40243</t>
+          <t>MG40259</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>ATARY DINOSAURIO MG40243</t>
+          <t>CARRO JET DESTAPADO MG40259</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -20673,35 +20673,40 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N441" t="n">
-        <v>520.674</v>
+        <v>1153.41</v>
       </c>
       <c r="O441" t="n">
-        <v>4165.392</v>
+        <v>2306.82</v>
       </c>
       <c r="P441" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="Q441" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>MG40259</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>CARRO JET DESTAPADO MG40259</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -20710,7 +20715,7 @@
         </is>
       </c>
       <c r="J442" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K442" t="n">
         <v>0</v>
@@ -20719,35 +20724,30 @@
         <v>0</v>
       </c>
       <c r="M442" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="N442" t="n">
-        <v>1153.41</v>
+        <v>2432.1356790123</v>
       </c>
       <c r="O442" t="n">
-        <v>2306.82</v>
+        <v>102149.6985185166</v>
       </c>
       <c r="P442" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="Q442" t="n">
-        <v>8000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40327</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>BLISTER PESCA STD  MG40327</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -20761,7 +20761,7 @@
         </is>
       </c>
       <c r="J443" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K443" t="n">
         <v>0</v>
@@ -20770,35 +20770,35 @@
         <v>0</v>
       </c>
       <c r="M443" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="N443" t="n">
-        <v>2432.1356790123</v>
+        <v>449.63</v>
       </c>
       <c r="O443" t="n">
-        <v>102149.6985185166</v>
+        <v>449.63</v>
       </c>
       <c r="P443" t="n">
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="Q443" t="n">
-        <v>189000</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>MG40327</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>BLISTER PESCA STD  MG40327</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="J444" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="K444" t="n">
         <v>0</v>
@@ -20816,30 +20816,30 @@
         <v>0</v>
       </c>
       <c r="M444" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="N444" t="n">
-        <v>449.63</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O444" t="n">
-        <v>449.63</v>
+        <v>53442.79357142789</v>
       </c>
       <c r="P444" t="n">
-        <v>5100</v>
+        <v>1200</v>
       </c>
       <c r="Q444" t="n">
-        <v>5100</v>
+        <v>282000</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40415</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>TELEFONO AVION MG40415</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -20862,35 +20862,35 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>235</v>
+        <v>2</v>
       </c>
       <c r="N445" t="n">
-        <v>227.41614285714</v>
+        <v>13308.19</v>
       </c>
       <c r="O445" t="n">
-        <v>53442.79357142789</v>
+        <v>26616.38</v>
       </c>
       <c r="P445" t="n">
-        <v>1200</v>
+        <v>34600</v>
       </c>
       <c r="Q445" t="n">
-        <v>282000</v>
+        <v>69200</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>MG40415</t>
+          <t>MG40570</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>TELEFONO AVION MG40415</t>
+          <t>REGISTRADORA SENCILLA MG40570</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -20899,7 +20899,7 @@
         </is>
       </c>
       <c r="J446" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K446" t="n">
         <v>0</v>
@@ -20908,35 +20908,35 @@
         <v>0</v>
       </c>
       <c r="M446" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N446" t="n">
-        <v>13308.19</v>
+        <v>8735.540000000001</v>
       </c>
       <c r="O446" t="n">
-        <v>26616.38</v>
+        <v>61148.78000000001</v>
       </c>
       <c r="P446" t="n">
-        <v>34600</v>
+        <v>29900</v>
       </c>
       <c r="Q446" t="n">
-        <v>69200</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MG40570</t>
+          <t>MG40805</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>REGISTRADORA SENCILLA MG40570</t>
+          <t>LANZA DARDOS HERO GDE MG40805</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -20945,7 +20945,7 @@
         </is>
       </c>
       <c r="J447" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K447" t="n">
         <v>0</v>
@@ -20954,35 +20954,35 @@
         <v>0</v>
       </c>
       <c r="M447" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N447" t="n">
-        <v>8735.540000000001</v>
+        <v>22654.34</v>
       </c>
       <c r="O447" t="n">
-        <v>61148.78000000001</v>
+        <v>249197.74</v>
       </c>
       <c r="P447" t="n">
-        <v>29900</v>
+        <v>58900</v>
       </c>
       <c r="Q447" t="n">
-        <v>209300</v>
+        <v>647900</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>MG40805</t>
+          <t>MG41038</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>LANZA DARDOS HERO GDE MG40805</t>
+          <t>VOLQUETA SENCILLA MED MG41038</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="J448" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K448" t="n">
         <v>0</v>
@@ -21000,35 +21000,35 @@
         <v>0</v>
       </c>
       <c r="M448" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N448" t="n">
-        <v>22654.34</v>
+        <v>4962.04</v>
       </c>
       <c r="O448" t="n">
-        <v>249197.74</v>
+        <v>9924.08</v>
       </c>
       <c r="P448" t="n">
-        <v>58900</v>
+        <v>12900</v>
       </c>
       <c r="Q448" t="n">
-        <v>647900</v>
+        <v>25800</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>MG41038</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>VOLQUETA SENCILLA MED MG41038</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="J449" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K449" t="n">
         <v>0</v>
@@ -21046,35 +21046,35 @@
         <v>0</v>
       </c>
       <c r="M449" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N449" t="n">
-        <v>4962.04</v>
+        <v>25110.1</v>
       </c>
       <c r="O449" t="n">
-        <v>9924.08</v>
+        <v>326431.3</v>
       </c>
       <c r="P449" t="n">
-        <v>12900</v>
+        <v>27900</v>
       </c>
       <c r="Q449" t="n">
-        <v>25800</v>
+        <v>362700</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MG41588</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -21083,7 +21083,7 @@
         </is>
       </c>
       <c r="J450" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K450" t="n">
         <v>0</v>
@@ -21092,30 +21092,30 @@
         <v>0</v>
       </c>
       <c r="M450" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N450" t="n">
-        <v>25110.1</v>
+        <v>5422.51</v>
       </c>
       <c r="O450" t="n">
-        <v>326431.3</v>
+        <v>32535.06</v>
       </c>
       <c r="P450" t="n">
-        <v>27900</v>
+        <v>19900</v>
       </c>
       <c r="Q450" t="n">
-        <v>362700</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>MG41588</t>
+          <t>MG41589</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>MUÑECA CONSULTORIO OFTALMOLOGICO CAJA MG41588</t>
+          <t>MUÑECA ODONTOLOGA MG41589</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -21129,7 +21129,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -21138,35 +21138,35 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N451" t="n">
-        <v>5422.51</v>
+        <v>5103.23</v>
       </c>
       <c r="O451" t="n">
-        <v>32535.06</v>
+        <v>20412.92</v>
       </c>
       <c r="P451" t="n">
         <v>19900</v>
       </c>
       <c r="Q451" t="n">
-        <v>119400</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>MG41589</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>MUÑECA ODONTOLOGA MG41589</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -21175,7 +21175,7 @@
         </is>
       </c>
       <c r="J452" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K452" t="n">
         <v>0</v>
@@ -21184,30 +21184,30 @@
         <v>0</v>
       </c>
       <c r="M452" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N452" t="n">
-        <v>5103.23</v>
+        <v>40500</v>
       </c>
       <c r="O452" t="n">
-        <v>20412.92</v>
+        <v>729000</v>
       </c>
       <c r="P452" t="n">
-        <v>19900</v>
+        <v>48600</v>
       </c>
       <c r="Q452" t="n">
-        <v>79600</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>MJC-558-1</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -21221,7 +21221,7 @@
         </is>
       </c>
       <c r="J453" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K453" t="n">
         <v>0</v>
@@ -21230,30 +21230,33 @@
         <v>0</v>
       </c>
       <c r="M453" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N453" t="n">
         <v>40500</v>
       </c>
       <c r="O453" t="n">
-        <v>729000</v>
+        <v>324000</v>
       </c>
       <c r="P453" t="n">
         <v>48600</v>
       </c>
       <c r="Q453" t="n">
-        <v>874800</v>
+        <v>388800</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
-        </is>
+          <t>MT4004</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -21263,11 +21266,11 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J454" t="n">
-        <v>8</v>
+        <v>582</v>
       </c>
       <c r="K454" t="n">
         <v>0</v>
@@ -21276,33 +21279,30 @@
         <v>0</v>
       </c>
       <c r="M454" t="n">
-        <v>8</v>
+        <v>582</v>
       </c>
       <c r="N454" t="n">
-        <v>40500</v>
+        <v>2539.5716920152</v>
       </c>
       <c r="O454" t="n">
-        <v>324000</v>
+        <v>1478030.724752846</v>
       </c>
       <c r="P454" t="n">
-        <v>48600</v>
+        <v>2900</v>
       </c>
       <c r="Q454" t="n">
-        <v>388800</v>
+        <v>1687800</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>MT4004</t>
-        </is>
-      </c>
-      <c r="B455" t="n">
-        <v>7700154271143</v>
+          <t>MT4690</t>
+        </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>BALDE CASTILLO PQÑ MT4690</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -21312,11 +21312,11 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J455" t="n">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="K455" t="n">
         <v>0</v>
@@ -21325,30 +21325,30 @@
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="N455" t="n">
-        <v>2539.5716920152</v>
+        <v>4687.9746748351</v>
       </c>
       <c r="O455" t="n">
-        <v>1478030.724752846</v>
+        <v>2629953.792582491</v>
       </c>
       <c r="P455" t="n">
-        <v>2900</v>
+        <v>5500</v>
       </c>
       <c r="Q455" t="n">
-        <v>1687800</v>
+        <v>3085500</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>MT4690</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>BALDE CASTILLO PQÑ MT4690</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="J456" t="n">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="K456" t="n">
         <v>0</v>
@@ -21371,35 +21371,35 @@
         <v>0</v>
       </c>
       <c r="M456" t="n">
-        <v>561</v>
+        <v>80</v>
       </c>
       <c r="N456" t="n">
-        <v>4687.974657277</v>
+        <v>4171.6685869565</v>
       </c>
       <c r="O456" t="n">
-        <v>2629953.782732397</v>
+        <v>333733.48695652</v>
       </c>
       <c r="P456" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="Q456" t="n">
-        <v>3085500</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>PT08</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
+          <t>ALCANCIA PEQUEÑA PP002</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -21420,32 +21420,32 @@
         <v>80</v>
       </c>
       <c r="N457" t="n">
-        <v>4171.6685954382</v>
+        <v>436.24</v>
       </c>
       <c r="O457" t="n">
-        <v>333733.487635056</v>
+        <v>34899.2</v>
       </c>
       <c r="P457" t="n">
-        <v>5000</v>
+        <v>550</v>
       </c>
       <c r="Q457" t="n">
-        <v>400000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>PT08</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>ALCANCIA PEQUEÑA PP002</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -21454,7 +21454,7 @@
         </is>
       </c>
       <c r="J458" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="K458" t="n">
         <v>0</v>
@@ -21463,35 +21463,40 @@
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="N458" t="n">
-        <v>436.24</v>
+        <v>1950.7</v>
       </c>
       <c r="O458" t="n">
-        <v>34899.2</v>
+        <v>206774.2</v>
       </c>
       <c r="P458" t="n">
-        <v>550</v>
+        <v>7500</v>
       </c>
       <c r="Q458" t="n">
-        <v>44000</v>
+        <v>795000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>PT15838</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>PT15838</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>LANZADORA DE AGUA PT15838</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -21500,7 +21505,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -21509,40 +21514,35 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="N459" t="n">
-        <v>1950.7</v>
+        <v>753.98</v>
       </c>
       <c r="O459" t="n">
-        <v>206774.2</v>
+        <v>753.98</v>
       </c>
       <c r="P459" t="n">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="Q459" t="n">
-        <v>795000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>PT15838</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>PT15838</t>
+          <t>PT25404</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>LANZADORA DE AGUA PT15838</t>
+          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>MONTABLES</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -21563,27 +21563,27 @@
         <v>1</v>
       </c>
       <c r="N460" t="n">
-        <v>753.98</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="O460" t="n">
-        <v>753.98</v>
+        <v>84538.46000000001</v>
       </c>
       <c r="P460" t="n">
-        <v>4000</v>
+        <v>109900</v>
       </c>
       <c r="Q460" t="n">
-        <v>4000</v>
+        <v>109900</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>PT25404</t>
+          <t>PT25419</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>MONOPATIN DE COLORES CON SILLA PT25404</t>
+          <t>MONOPATIN CAJA LUCES PT25419</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -21597,7 +21597,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -21606,30 +21606,30 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N461" t="n">
-        <v>84538.46000000001</v>
+        <v>87920</v>
       </c>
       <c r="O461" t="n">
-        <v>84538.46000000001</v>
+        <v>527520</v>
       </c>
       <c r="P461" t="n">
         <v>109900</v>
       </c>
       <c r="Q461" t="n">
-        <v>109900</v>
+        <v>659400</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>PT25419</t>
+          <t>PT25420</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>MONOPATIN CAJA LUCES PT25419</t>
+          <t>MONOPATIN  PATO PT25420</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -21643,7 +21643,7 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
@@ -21652,35 +21652,35 @@
         <v>0</v>
       </c>
       <c r="M462" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N462" t="n">
-        <v>87920</v>
+        <v>15394.79</v>
       </c>
       <c r="O462" t="n">
-        <v>527520</v>
+        <v>169342.69</v>
       </c>
       <c r="P462" t="n">
-        <v>109900</v>
+        <v>99800</v>
       </c>
       <c r="Q462" t="n">
-        <v>659400</v>
+        <v>1097800</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>PT25420</t>
+          <t>PT26747</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>MONOPATIN  PATO PT25420</t>
+          <t>TABLA LABERINTO PT26747</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>MONTABLES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -21689,7 +21689,7 @@
         </is>
       </c>
       <c r="J463" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K463" t="n">
         <v>0</v>
@@ -21698,30 +21698,30 @@
         <v>0</v>
       </c>
       <c r="M463" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N463" t="n">
-        <v>15394.79</v>
+        <v>2361.5097058824</v>
       </c>
       <c r="O463" t="n">
-        <v>169342.69</v>
+        <v>56676.2329411776</v>
       </c>
       <c r="P463" t="n">
-        <v>99800</v>
+        <v>6200</v>
       </c>
       <c r="Q463" t="n">
-        <v>1097800</v>
+        <v>148800</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>PT26747</t>
+          <t>RL589-28D</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>TABLA LABERINTO PT26747</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -21747,27 +21747,27 @@
         <v>24</v>
       </c>
       <c r="N464" t="n">
-        <v>2361.5097058824</v>
+        <v>7046.7392307692</v>
       </c>
       <c r="O464" t="n">
-        <v>56676.2329411776</v>
+        <v>169121.7415384608</v>
       </c>
       <c r="P464" t="n">
-        <v>6200</v>
+        <v>22900</v>
       </c>
       <c r="Q464" t="n">
-        <v>148800</v>
+        <v>549600</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>RL589-28D</t>
+          <t>RL589-33D</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-28D</t>
+          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="J465" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K465" t="n">
         <v>0</v>
@@ -21790,35 +21790,35 @@
         <v>0</v>
       </c>
       <c r="M465" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="N465" t="n">
-        <v>7046.7392307692</v>
+        <v>10009.172222222</v>
       </c>
       <c r="O465" t="n">
-        <v>169121.7415384608</v>
+        <v>30027.516666666</v>
       </c>
       <c r="P465" t="n">
         <v>22900</v>
       </c>
       <c r="Q465" t="n">
-        <v>549600</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>RL589-33D</t>
+          <t>SEBQ04</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>JUGUETE CARRO DEPORTIVO R/C RL589-33D</t>
+          <t>TORRES DE ABACO SE1428</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="J466" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K466" t="n">
         <v>0</v>
@@ -21836,35 +21836,35 @@
         <v>0</v>
       </c>
       <c r="M466" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N466" t="n">
-        <v>10009.172222222</v>
+        <v>4091.4</v>
       </c>
       <c r="O466" t="n">
-        <v>30027.516666666</v>
+        <v>36822.6</v>
       </c>
       <c r="P466" t="n">
-        <v>22900</v>
+        <v>10000</v>
       </c>
       <c r="Q466" t="n">
-        <v>68700</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>SEBQ04</t>
+          <t>SEBQ17</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428</t>
+          <t>CUBO MAGICO COLORES X5 SE-19126</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -21873,7 +21873,7 @@
         </is>
       </c>
       <c r="J467" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="K467" t="n">
         <v>0</v>
@@ -21882,35 +21882,35 @@
         <v>0</v>
       </c>
       <c r="M467" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="N467" t="n">
-        <v>4091.4</v>
+        <v>5148.77</v>
       </c>
       <c r="O467" t="n">
-        <v>36822.6</v>
+        <v>278033.58</v>
       </c>
       <c r="P467" t="n">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="Q467" t="n">
-        <v>90000</v>
+        <v>567000</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>SEBQ17</t>
+          <t>SEBQ27</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>CUBO MAGICO COLORES X5 SE-19126</t>
+          <t>CELULAR MUÑECO X12 SE1597</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="J468" t="n">
-        <v>54</v>
+        <v>451</v>
       </c>
       <c r="K468" t="n">
         <v>0</v>
@@ -21928,30 +21928,30 @@
         <v>0</v>
       </c>
       <c r="M468" t="n">
-        <v>54</v>
+        <v>451</v>
       </c>
       <c r="N468" t="n">
-        <v>5148.77</v>
+        <v>855.85</v>
       </c>
       <c r="O468" t="n">
-        <v>278033.58</v>
+        <v>385988.35</v>
       </c>
       <c r="P468" t="n">
-        <v>10500</v>
+        <v>3500</v>
       </c>
       <c r="Q468" t="n">
-        <v>567000</v>
+        <v>1578500</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SEBQ27</t>
+          <t>SLT052</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>CELULAR MUÑECO X12 SE1597</t>
+          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -21965,7 +21965,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -21974,35 +21974,35 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="N469" t="n">
-        <v>855.85</v>
+        <v>0</v>
       </c>
       <c r="O469" t="n">
-        <v>385988.35</v>
+        <v>0</v>
       </c>
       <c r="P469" t="n">
-        <v>3500</v>
+        <v>13500</v>
       </c>
       <c r="Q469" t="n">
-        <v>1578500</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>SLT052</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>JUGUETE SET DINOSAURIO HUEVO X 6  6216</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -22011,7 +22011,7 @@
         </is>
       </c>
       <c r="J470" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="K470" t="n">
         <v>0</v>
@@ -22020,30 +22020,30 @@
         <v>0</v>
       </c>
       <c r="M470" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="N470" t="n">
-        <v>0</v>
+        <v>4550</v>
       </c>
       <c r="O470" t="n">
-        <v>0</v>
+        <v>819000</v>
       </c>
       <c r="P470" t="n">
-        <v>13500</v>
+        <v>5500</v>
       </c>
       <c r="Q470" t="n">
-        <v>27000</v>
+        <v>990000</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT2641</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>BALON BASQUEBOL # 5 SLT2641</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -22057,7 +22057,7 @@
         </is>
       </c>
       <c r="J471" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="K471" t="n">
         <v>0</v>
@@ -22066,30 +22066,30 @@
         <v>0</v>
       </c>
       <c r="M471" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="N471" t="n">
-        <v>4550</v>
+        <v>422.91</v>
       </c>
       <c r="O471" t="n">
-        <v>819000</v>
+        <v>3383.28</v>
       </c>
       <c r="P471" t="n">
-        <v>5500</v>
+        <v>12500</v>
       </c>
       <c r="Q471" t="n">
-        <v>990000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>SLT2641</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 5 SLT2641</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -22112,30 +22112,30 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="N472" t="n">
-        <v>422.91</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O472" t="n">
-        <v>3383.28</v>
+        <v>58314.66528688533</v>
       </c>
       <c r="P472" t="n">
-        <v>12500</v>
+        <v>14500</v>
       </c>
       <c r="Q472" t="n">
-        <v>100000</v>
+        <v>2479500</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SLT2642</t>
+          <t>SLT2714</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
+          <t>VENTILADOR MINI SLT2714</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -22149,7 +22149,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -22158,35 +22158,35 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>171</v>
+        <v>32</v>
       </c>
       <c r="N473" t="n">
-        <v>341.02143442623</v>
+        <v>4158.2957575758</v>
       </c>
       <c r="O473" t="n">
-        <v>58314.66528688533</v>
+        <v>133065.4642424256</v>
       </c>
       <c r="P473" t="n">
-        <v>14500</v>
+        <v>13800</v>
       </c>
       <c r="Q473" t="n">
-        <v>2479500</v>
+        <v>441600</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SLT2714</t>
+          <t>T018</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>VENTILADOR MINI SLT2714</t>
+          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -22204,30 +22204,30 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N474" t="n">
-        <v>4158.2957575758</v>
+        <v>22230.77</v>
       </c>
       <c r="O474" t="n">
-        <v>133065.4642424256</v>
+        <v>111153.85</v>
       </c>
       <c r="P474" t="n">
-        <v>13800</v>
+        <v>28900</v>
       </c>
       <c r="Q474" t="n">
-        <v>441600</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>T018</t>
+          <t>T032</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE LUCES Y SONIDOS ZXW-30</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -22241,7 +22241,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -22250,30 +22250,30 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N475" t="n">
-        <v>22230.77</v>
+        <v>33200</v>
       </c>
       <c r="O475" t="n">
-        <v>111153.85</v>
+        <v>33200</v>
       </c>
       <c r="P475" t="n">
-        <v>28900</v>
+        <v>41500</v>
       </c>
       <c r="Q475" t="n">
-        <v>144500</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>T032</t>
+          <t>T038</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60/T032</t>
+          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -22299,32 +22299,32 @@
         <v>1</v>
       </c>
       <c r="N476" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="O476" t="n">
-        <v>33200</v>
+        <v>4962.04</v>
       </c>
       <c r="P476" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
       <c r="Q476" t="n">
-        <v>41500</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>T038</t>
+          <t>T046</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>PELUCHE SESAMO,POOH,NARUTO,DUMBO ZMJ-20/WN-20/HY-20/XFX-20</t>
+          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -22333,7 +22333,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -22342,35 +22342,35 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N477" t="n">
-        <v>4962.04</v>
+        <v>22802.48</v>
       </c>
       <c r="O477" t="n">
-        <v>4962.04</v>
+        <v>68407.44</v>
       </c>
       <c r="P477" t="n">
-        <v>12900</v>
+        <v>41500</v>
       </c>
       <c r="Q477" t="n">
-        <v>12900</v>
+        <v>124500</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>T046</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>JUGUETE PATRULLA CAMINADORA GLX-20</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -22379,7 +22379,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -22388,35 +22388,35 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N478" t="n">
-        <v>22802.484</v>
+        <v>12392.16</v>
       </c>
       <c r="O478" t="n">
-        <v>114012.42</v>
+        <v>557647.2</v>
       </c>
       <c r="P478" t="n">
-        <v>41500</v>
+        <v>15900</v>
       </c>
       <c r="Q478" t="n">
-        <v>207500</v>
+        <v>715500</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -22425,7 +22425,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -22434,35 +22434,35 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="N479" t="n">
-        <v>12392.16</v>
+        <v>24882.58</v>
       </c>
       <c r="O479" t="n">
-        <v>557647.2</v>
+        <v>174178.06</v>
       </c>
       <c r="P479" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q479" t="n">
-        <v>715500</v>
+        <v>220500</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T066</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -22471,7 +22471,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -22480,30 +22480,30 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N480" t="n">
-        <v>24882.58</v>
+        <v>16576.2</v>
       </c>
       <c r="O480" t="n">
-        <v>174178.06</v>
+        <v>16576.2</v>
       </c>
       <c r="P480" t="n">
-        <v>31500</v>
+        <v>25900</v>
       </c>
       <c r="Q480" t="n">
-        <v>220500</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>T066</t>
+          <t>T067</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>PELUCHE SILVESTRE PILIN-TOM-JERRY HM-25</t>
+          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -22529,27 +22529,27 @@
         <v>1</v>
       </c>
       <c r="N481" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="O481" t="n">
-        <v>16576.2</v>
+        <v>47600</v>
       </c>
       <c r="P481" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
       <c r="Q481" t="n">
-        <v>25900</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>T067</t>
+          <t>T073</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>PELUCHE MECANICO DINOSAURIO BL-235</t>
+          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -22563,7 +22563,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -22572,30 +22572,30 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N482" t="n">
-        <v>47600</v>
+        <v>6102.9</v>
       </c>
       <c r="O482" t="n">
-        <v>47600</v>
+        <v>12205.8</v>
       </c>
       <c r="P482" t="n">
-        <v>59500</v>
+        <v>11900</v>
       </c>
       <c r="Q482" t="n">
-        <v>59500</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>T073</t>
+          <t>T079</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>PELUCHE BOLISTA PERSONAJE 25CM QQ-20</t>
+          <t>PELUCHE 15CM BQ-15</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -22609,7 +22609,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -22618,30 +22618,30 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="N483" t="n">
-        <v>6102.9</v>
+        <v>525.33</v>
       </c>
       <c r="O483" t="n">
-        <v>12205.8</v>
+        <v>12082.59</v>
       </c>
       <c r="P483" t="n">
-        <v>11900</v>
+        <v>5900</v>
       </c>
       <c r="Q483" t="n">
-        <v>23800</v>
+        <v>135700</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>T079</t>
+          <t>T089</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PELUCHE 15CM BQ-15</t>
+          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -22664,30 +22664,30 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N484" t="n">
-        <v>525.33</v>
+        <v>8580.75</v>
       </c>
       <c r="O484" t="n">
-        <v>12082.59</v>
+        <v>17161.5</v>
       </c>
       <c r="P484" t="n">
-        <v>5900</v>
+        <v>42900</v>
       </c>
       <c r="Q484" t="n">
-        <v>135700</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>T089</t>
+          <t>T098</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
+          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -22701,7 +22701,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22710,30 +22710,30 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N485" t="n">
-        <v>8580.75</v>
+        <v>14308.02</v>
       </c>
       <c r="O485" t="n">
-        <v>17161.5</v>
+        <v>14308.02</v>
       </c>
       <c r="P485" t="n">
-        <v>42900</v>
+        <v>27900</v>
       </c>
       <c r="Q485" t="n">
-        <v>85800</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>T098</t>
+          <t>T099</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>PELUCHE GATO SENTADO 30CM XGAT-30</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22756,30 +22756,30 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N486" t="n">
-        <v>14308.02</v>
+        <v>8538.8633333333</v>
       </c>
       <c r="O486" t="n">
-        <v>14308.02</v>
+        <v>17077.7266666666</v>
       </c>
       <c r="P486" t="n">
-        <v>27900</v>
+        <v>18500</v>
       </c>
       <c r="Q486" t="n">
-        <v>27900</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>T099</t>
+          <t>T103</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9/T099</t>
+          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -22793,7 +22793,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -22802,30 +22802,30 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N487" t="n">
-        <v>8538.8633333333</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O487" t="n">
-        <v>17077.7266666666</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="P487" t="n">
-        <v>18500</v>
+        <v>25900</v>
       </c>
       <c r="Q487" t="n">
-        <v>37000</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>T103</t>
+          <t>T117</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PELUCHE GATO MULTICOLOR 30CM DT210374-30</t>
+          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -22851,27 +22851,27 @@
         <v>1</v>
       </c>
       <c r="N488" t="n">
-        <v>9962.040000000001</v>
+        <v>14577.42</v>
       </c>
       <c r="O488" t="n">
-        <v>9962.040000000001</v>
+        <v>14577.42</v>
       </c>
       <c r="P488" t="n">
-        <v>25900</v>
+        <v>37900</v>
       </c>
       <c r="Q488" t="n">
-        <v>25900</v>
+        <v>37900</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>T117</t>
+          <t>T121</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>PELUCHE GATA MERIE 45CM MLM-30</t>
+          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22894,30 +22894,30 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N489" t="n">
-        <v>14577.42</v>
+        <v>13000.5</v>
       </c>
       <c r="O489" t="n">
-        <v>29154.84</v>
+        <v>13000.5</v>
       </c>
       <c r="P489" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="Q489" t="n">
-        <v>75800</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>T121</t>
+          <t>T135</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 30CM 3468/30</t>
+          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -22931,7 +22931,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -22940,30 +22940,30 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N490" t="n">
-        <v>13000.5</v>
+        <v>7115.88</v>
       </c>
       <c r="O490" t="n">
-        <v>13000.5</v>
+        <v>35579.4</v>
       </c>
       <c r="P490" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q490" t="n">
-        <v>32500</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>T135</t>
+          <t>T136</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRICO CON GORRO 20CM XZK-15</t>
+          <t>BOLSO PELUCHE ANIMALES P01-30</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -22977,7 +22977,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22986,30 +22986,30 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N491" t="n">
-        <v>7115.88</v>
+        <v>7886.43</v>
       </c>
       <c r="O491" t="n">
-        <v>35579.4</v>
+        <v>31545.72</v>
       </c>
       <c r="P491" t="n">
-        <v>18500</v>
+        <v>34500</v>
       </c>
       <c r="Q491" t="n">
-        <v>92500</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>T136</t>
+          <t>T143</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>BOLSO PELUCHE ANIMALES P01-30</t>
+          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -23032,30 +23032,30 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N492" t="n">
-        <v>7886.43</v>
+        <v>23920</v>
       </c>
       <c r="O492" t="n">
-        <v>31545.72</v>
+        <v>23920</v>
       </c>
       <c r="P492" t="n">
-        <v>34500</v>
+        <v>29900</v>
       </c>
       <c r="Q492" t="n">
-        <v>138000</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>T143</t>
+          <t>T157</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM CHALECO LNQ-30</t>
+          <t>PELUCHE CONEJO 30CM ANA-28</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -23069,7 +23069,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -23078,30 +23078,30 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N493" t="n">
-        <v>23920</v>
+        <v>11472.4</v>
       </c>
       <c r="O493" t="n">
-        <v>23920</v>
+        <v>34417.2</v>
       </c>
       <c r="P493" t="n">
-        <v>29900</v>
+        <v>23900</v>
       </c>
       <c r="Q493" t="n">
-        <v>29900</v>
+        <v>71700</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>T157</t>
+          <t>T158</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>PELUCHE CONEJO 30CM ANA-28</t>
+          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -23124,30 +23124,30 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N494" t="n">
-        <v>11472.4</v>
+        <v>10577.42</v>
       </c>
       <c r="O494" t="n">
-        <v>34417.2</v>
+        <v>105774.2</v>
       </c>
       <c r="P494" t="n">
-        <v>23900</v>
+        <v>27500</v>
       </c>
       <c r="Q494" t="n">
-        <v>71700</v>
+        <v>275000</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>T158</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>PELUCHE TITERE DINOSAURIO 30CM SO-25</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -23161,7 +23161,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -23170,30 +23170,30 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N495" t="n">
-        <v>10577.42</v>
+        <v>5186.45</v>
       </c>
       <c r="O495" t="n">
-        <v>105774.2</v>
+        <v>103729</v>
       </c>
       <c r="P495" t="n">
-        <v>27500</v>
+        <v>7200</v>
       </c>
       <c r="Q495" t="n">
-        <v>275000</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T171</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -23207,7 +23207,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -23216,44 +23216,34 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N496" t="n">
-        <v>5186.45</v>
+        <v>14832.4</v>
       </c>
       <c r="O496" t="n">
-        <v>103729</v>
+        <v>14832.4</v>
       </c>
       <c r="P496" t="n">
-        <v>7200</v>
+        <v>30900</v>
       </c>
       <c r="Q496" t="n">
-        <v>144000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>T171</t>
+          <t>T172</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE OJOS BORDADOS 35CM GGH-35</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
         </is>
       </c>
       <c r="J497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -23262,34 +23252,44 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N497" t="n">
-        <v>14832.4</v>
+        <v>4462.14</v>
       </c>
       <c r="O497" t="n">
-        <v>14832.4</v>
+        <v>8924.280000000001</v>
       </c>
       <c r="P497" t="n">
-        <v>30900</v>
+        <v>14500</v>
       </c>
       <c r="Q497" t="n">
-        <v>30900</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>T172</t>
+          <t>T175</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>PELUCHE MOSTRUO 20CM BFG-8</t>
+          <t>PELUCHE BOWSER 35CM KUP-35</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J498" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -23298,30 +23298,30 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N498" t="n">
-        <v>4462.14</v>
+        <v>4614.22</v>
       </c>
       <c r="O498" t="n">
-        <v>8924.280000000001</v>
+        <v>32299.54</v>
       </c>
       <c r="P498" t="n">
-        <v>14500</v>
+        <v>51900</v>
       </c>
       <c r="Q498" t="n">
-        <v>29000</v>
+        <v>363300</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>T175</t>
+          <t>T181</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>PELUCHE BOWSER 35CM KUP-35</t>
+          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -23335,7 +23335,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -23344,30 +23344,30 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N499" t="n">
-        <v>4614.22</v>
+        <v>11692.75</v>
       </c>
       <c r="O499" t="n">
-        <v>32299.54</v>
+        <v>23385.5</v>
       </c>
       <c r="P499" t="n">
-        <v>51900</v>
+        <v>28500</v>
       </c>
       <c r="Q499" t="n">
-        <v>363300</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>T181</t>
+          <t>T182</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PELUCHE LUIGI SENTADO 30CM MAR-25SEN</t>
+          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -23381,7 +23381,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -23390,30 +23390,30 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N500" t="n">
-        <v>11692.75</v>
+        <v>5600.5</v>
       </c>
       <c r="O500" t="n">
-        <v>23385.5</v>
+        <v>5600.5</v>
       </c>
       <c r="P500" t="n">
-        <v>28500</v>
+        <v>14000</v>
       </c>
       <c r="Q500" t="n">
-        <v>57000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>T182</t>
+          <t>T185</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
+          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -23427,7 +23427,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -23436,30 +23436,30 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N501" t="n">
-        <v>5600.5</v>
+        <v>9160.5</v>
       </c>
       <c r="O501" t="n">
-        <v>5600.5</v>
+        <v>45802.5</v>
       </c>
       <c r="P501" t="n">
-        <v>14000</v>
+        <v>22900</v>
       </c>
       <c r="Q501" t="n">
-        <v>14000</v>
+        <v>114500</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>T185</t>
+          <t>T195</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>COBIJITA PERSONAJES TZ-1-5-7</t>
+          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -23473,7 +23473,7 @@
         </is>
       </c>
       <c r="J502" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23482,30 +23482,30 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N502" t="n">
-        <v>9160.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="O502" t="n">
-        <v>45802.5</v>
+        <v>9192.809999999999</v>
       </c>
       <c r="P502" t="n">
-        <v>22900</v>
+        <v>23900</v>
       </c>
       <c r="Q502" t="n">
-        <v>114500</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>T195</t>
+          <t>T201-LJ</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>PELUCHE PANDA SUPER HEROES LMXM-30</t>
+          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
@@ -23519,7 +23519,7 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -23528,35 +23528,35 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N503" t="n">
-        <v>9192.809999999999</v>
+        <v>35000</v>
       </c>
       <c r="O503" t="n">
-        <v>9192.809999999999</v>
+        <v>70000</v>
       </c>
       <c r="P503" t="n">
-        <v>23900</v>
+        <v>45500</v>
       </c>
       <c r="Q503" t="n">
-        <v>23900</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>T201-LJ</t>
+          <t>T203</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>PELUCHE OSO VESTIDO 40CM LH6266-40</t>
+          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23574,30 +23574,30 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N504" t="n">
-        <v>35000</v>
+        <v>11885.11</v>
       </c>
       <c r="O504" t="n">
-        <v>70000</v>
+        <v>11885.11</v>
       </c>
       <c r="P504" t="n">
-        <v>45500</v>
+        <v>30900</v>
       </c>
       <c r="Q504" t="n">
-        <v>91000</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>T203</t>
+          <t>T206</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>PELUCHE LUZ Y SONIDO 30CM LUZ-30/T203</t>
+          <t>PELUCHE PATO 30CM HJE-30</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -23623,32 +23623,32 @@
         <v>1</v>
       </c>
       <c r="N505" t="n">
-        <v>11885.11</v>
+        <v>31120</v>
       </c>
       <c r="O505" t="n">
-        <v>11885.11</v>
+        <v>31120</v>
       </c>
       <c r="P505" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
       <c r="Q505" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>T206</t>
+          <t>T207</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>PELUCHE PATO 30CM HJE-30</t>
+          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -23669,27 +23669,27 @@
         <v>2</v>
       </c>
       <c r="N506" t="n">
-        <v>31120</v>
+        <v>7520.71</v>
       </c>
       <c r="O506" t="n">
-        <v>62240</v>
+        <v>15041.42</v>
       </c>
       <c r="P506" t="n">
-        <v>38900</v>
+        <v>32900</v>
       </c>
       <c r="Q506" t="n">
-        <v>77800</v>
+        <v>65800</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>T207</t>
+          <t>T211</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 35CM GZS-35</t>
+          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
@@ -23715,27 +23715,27 @@
         <v>2</v>
       </c>
       <c r="N507" t="n">
-        <v>7520.71</v>
+        <v>16500.5</v>
       </c>
       <c r="O507" t="n">
-        <v>15041.42</v>
+        <v>33001</v>
       </c>
       <c r="P507" t="n">
-        <v>32900</v>
+        <v>42900</v>
       </c>
       <c r="Q507" t="n">
-        <v>65800</v>
+        <v>85800</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>T211</t>
+          <t>T213</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>PELUCHE GATO BOLSILLOS 40CM WJM-40</t>
+          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23758,30 +23758,30 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N508" t="n">
-        <v>16500.5</v>
+        <v>16220.2125</v>
       </c>
       <c r="O508" t="n">
-        <v>33001</v>
+        <v>64880.85</v>
       </c>
       <c r="P508" t="n">
-        <v>42900</v>
+        <v>36900</v>
       </c>
       <c r="Q508" t="n">
-        <v>85800</v>
+        <v>147600</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>T213</t>
+          <t>T214</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO CANTANTE 40CM PCO-40</t>
+          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -23795,7 +23795,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23804,30 +23804,30 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N509" t="n">
-        <v>16220.2125</v>
+        <v>11885.11</v>
       </c>
       <c r="O509" t="n">
-        <v>64880.85</v>
+        <v>11885.11</v>
       </c>
       <c r="P509" t="n">
-        <v>36900</v>
+        <v>30900</v>
       </c>
       <c r="Q509" t="n">
-        <v>147600</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>T214</t>
+          <t>T216</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>PELUCHE TORO TIERNO 40CM 8562-38</t>
+          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
@@ -23841,7 +23841,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23850,30 +23850,30 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N510" t="n">
-        <v>11885.11</v>
+        <v>14760.5</v>
       </c>
       <c r="O510" t="n">
-        <v>11885.11</v>
+        <v>73802.5</v>
       </c>
       <c r="P510" t="n">
-        <v>30900</v>
+        <v>36900</v>
       </c>
       <c r="Q510" t="n">
-        <v>30900</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>T216</t>
+          <t>T217</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO GDE 50CM SUR05-50/T216</t>
+          <t>PELUCHE GATO TELA 30CM BQM-30</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
@@ -23887,7 +23887,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23896,44 +23896,34 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N511" t="n">
-        <v>14760.5</v>
+        <v>8462.040000000001</v>
       </c>
       <c r="O511" t="n">
-        <v>73802.5</v>
+        <v>50772.24000000001</v>
       </c>
       <c r="P511" t="n">
-        <v>36900</v>
+        <v>22000</v>
       </c>
       <c r="Q511" t="n">
-        <v>184500</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>T217</t>
+          <t>T222</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>PELUCHE GATO TELA 30CM BQM-30</t>
-        </is>
-      </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
-        </is>
-      </c>
-      <c r="I512" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
         </is>
       </c>
       <c r="J512" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23942,30 +23932,40 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N512" t="n">
-        <v>8462.040000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="O512" t="n">
-        <v>50772.24000000001</v>
+        <v>23461.54</v>
       </c>
       <c r="P512" t="n">
-        <v>22000</v>
+        <v>30500</v>
       </c>
       <c r="Q512" t="n">
-        <v>132000</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>T222</t>
+          <t>T229</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>PELUCHE PERRO SENTADO 30CM PC-30T-SUR</t>
+          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J513" t="n">
@@ -23981,27 +23981,27 @@
         <v>1</v>
       </c>
       <c r="N513" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="O513" t="n">
-        <v>23461.54</v>
+        <v>18600.5</v>
       </c>
       <c r="P513" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
       <c r="Q513" t="n">
-        <v>30500</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>T229</t>
+          <t>T243</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>PELUCHE POLLO GORRO 45CM XY-45</t>
+          <t>PELUCHE GATO 40CM DX-60</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -24027,27 +24027,27 @@
         <v>1</v>
       </c>
       <c r="N514" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="O514" t="n">
-        <v>18600.5</v>
+        <v>26000</v>
       </c>
       <c r="P514" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
       <c r="Q514" t="n">
-        <v>46500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>T243</t>
+          <t>T244</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>PELUCHE GATO 40CM DX-60</t>
+          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -24061,7 +24061,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -24070,30 +24070,30 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N515" t="n">
-        <v>26000</v>
+        <v>7400.5</v>
       </c>
       <c r="O515" t="n">
-        <v>26000</v>
+        <v>22201.5</v>
       </c>
       <c r="P515" t="n">
-        <v>32500</v>
+        <v>18500</v>
       </c>
       <c r="Q515" t="n">
-        <v>32500</v>
+        <v>55500</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>T244</t>
+          <t>T245</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>PELUCHE POCILLO COJIN 30CM DT210464-9</t>
+          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -24116,30 +24116,30 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N516" t="n">
-        <v>7400.5</v>
+        <v>25200</v>
       </c>
       <c r="O516" t="n">
-        <v>22201.5</v>
+        <v>25200</v>
       </c>
       <c r="P516" t="n">
-        <v>18500</v>
+        <v>31500</v>
       </c>
       <c r="Q516" t="n">
-        <v>55500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>T245</t>
+          <t>T247</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>PELUCHE OSO ROPA NEON 40CM 5011-40/T245</t>
+          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -24153,7 +24153,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -24162,30 +24162,30 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N517" t="n">
-        <v>25200</v>
+        <v>8667.34</v>
       </c>
       <c r="O517" t="n">
-        <v>25200</v>
+        <v>34669.36</v>
       </c>
       <c r="P517" t="n">
-        <v>31500</v>
+        <v>32500</v>
       </c>
       <c r="Q517" t="n">
-        <v>31500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>T247</t>
+          <t>T248</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS35CM GZS-35</t>
+          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -24199,7 +24199,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -24208,30 +24208,30 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N518" t="n">
-        <v>8667.34</v>
+        <v>40720</v>
       </c>
       <c r="O518" t="n">
-        <v>34669.36</v>
+        <v>81440</v>
       </c>
       <c r="P518" t="n">
-        <v>32500</v>
+        <v>50900</v>
       </c>
       <c r="Q518" t="n">
-        <v>130000</v>
+        <v>101800</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>T248</t>
+          <t>T250</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>PELUCHE TIGRE BOLSILLOS 45CM GZS-45</t>
+          <t>PELUCHE MAGO 40CM PCO-40</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="J519" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -24254,30 +24254,30 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N519" t="n">
-        <v>40720</v>
+        <v>29520</v>
       </c>
       <c r="O519" t="n">
-        <v>81440</v>
+        <v>88560</v>
       </c>
       <c r="P519" t="n">
-        <v>50900</v>
+        <v>36900</v>
       </c>
       <c r="Q519" t="n">
-        <v>101800</v>
+        <v>110700</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>T250</t>
+          <t>T272</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>PELUCHE MAGO 40CM PCO-40</t>
+          <t>PELUCHE BUHO 40CM MTY-40</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
@@ -24291,7 +24291,7 @@
         </is>
       </c>
       <c r="J520" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -24300,30 +24300,30 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N520" t="n">
-        <v>29520</v>
+        <v>12500.5</v>
       </c>
       <c r="O520" t="n">
-        <v>88560</v>
+        <v>12500.5</v>
       </c>
       <c r="P520" t="n">
-        <v>36900</v>
+        <v>32500</v>
       </c>
       <c r="Q520" t="n">
-        <v>110700</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>T272</t>
+          <t>T273</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>PELUCHE BUHO 40CM MTY-40</t>
+          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -24349,37 +24349,27 @@
         <v>1</v>
       </c>
       <c r="N521" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="O521" t="n">
-        <v>12500.5</v>
+        <v>13808.19</v>
       </c>
       <c r="P521" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
       <c r="Q521" t="n">
-        <v>32500</v>
+        <v>35900</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>T273</t>
+          <t>T300</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMALES 30CM SENTADO 4386-30</t>
-        </is>
-      </c>
-      <c r="E522" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I522" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
         </is>
       </c>
       <c r="J522" t="n">
@@ -24395,31 +24385,31 @@
         <v>1</v>
       </c>
       <c r="N522" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="O522" t="n">
-        <v>13808.19</v>
+        <v>13686.31</v>
       </c>
       <c r="P522" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
       <c r="Q522" t="n">
-        <v>35900</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>T300</t>
+          <t>T334</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE MUSICA Y LUZ 25CM 9901-3</t>
+          <t>PELUCHE DIGIMON 20CM MD-20</t>
         </is>
       </c>
       <c r="J523" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -24428,34 +24418,34 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N523" t="n">
-        <v>13686.31</v>
+        <v>7571.81</v>
       </c>
       <c r="O523" t="n">
-        <v>13686.31</v>
+        <v>45430.86</v>
       </c>
       <c r="P523" t="n">
-        <v>30500</v>
+        <v>15900</v>
       </c>
       <c r="Q523" t="n">
-        <v>30500</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>T334</t>
+          <t>T336</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>PELUCHE DIGIMON 20CM MD-20</t>
+          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
         </is>
       </c>
       <c r="J524" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -24464,34 +24454,44 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N524" t="n">
-        <v>7571.81</v>
+        <v>9962.040000000001</v>
       </c>
       <c r="O524" t="n">
-        <v>45430.86</v>
+        <v>19924.08</v>
       </c>
       <c r="P524" t="n">
-        <v>15900</v>
+        <v>25900</v>
       </c>
       <c r="Q524" t="n">
-        <v>95400</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>T336</t>
+          <t>T345</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>PELUCHE MASCOTA NARUTO 25CM ZR-18</t>
+          <t>PELUCHE ADVNG 20CM ESP-20</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24500,35 +24500,30 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N525" t="n">
-        <v>9962.040000000001</v>
+        <v>1250.88</v>
       </c>
       <c r="O525" t="n">
-        <v>19924.08</v>
+        <v>3752.64</v>
       </c>
       <c r="P525" t="n">
-        <v>25900</v>
+        <v>12500</v>
       </c>
       <c r="Q525" t="n">
-        <v>51800</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>T345</t>
+          <t>T352</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>PELUCHE ADVNG 20CM ESP-20</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>NINJA T352</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -24537,7 +24532,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24546,30 +24541,35 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N526" t="n">
-        <v>1250.88</v>
+        <v>5192.31</v>
       </c>
       <c r="O526" t="n">
-        <v>3752.64</v>
+        <v>5192.31</v>
       </c>
       <c r="P526" t="n">
-        <v>12500</v>
+        <v>13500</v>
       </c>
       <c r="Q526" t="n">
-        <v>37500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>T352</t>
+          <t>TB058</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>NINJA T352</t>
+          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -24578,7 +24578,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24587,35 +24587,35 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N527" t="n">
-        <v>5192.31</v>
+        <v>17159.86</v>
       </c>
       <c r="O527" t="n">
-        <v>5192.31</v>
+        <v>51479.58</v>
       </c>
       <c r="P527" t="n">
-        <v>13500</v>
+        <v>21900</v>
       </c>
       <c r="Q527" t="n">
-        <v>13500</v>
+        <v>65700</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>TB058</t>
+          <t>TO-030</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>PELUCHE HAPPY BIRTHDAY GDE DT170763-25</t>
+          <t>COJIN ANIMALES 40CM DWKD-40</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -24624,7 +24624,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24633,30 +24633,30 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N528" t="n">
-        <v>17159.86</v>
+        <v>18384.62</v>
       </c>
       <c r="O528" t="n">
-        <v>51479.58</v>
+        <v>18384.62</v>
       </c>
       <c r="P528" t="n">
-        <v>21900</v>
+        <v>23900</v>
       </c>
       <c r="Q528" t="n">
-        <v>65700</v>
+        <v>23900</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>TO-030</t>
+          <t>TO-038</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>COJIN ANIMALES 40CM DWKD-40</t>
+          <t>COJIN ANIMAL 30CM DXS-25</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24682,27 +24682,27 @@
         <v>1</v>
       </c>
       <c r="N529" t="n">
-        <v>18384.62</v>
+        <v>14800</v>
       </c>
       <c r="O529" t="n">
-        <v>18384.62</v>
+        <v>14800</v>
       </c>
       <c r="P529" t="n">
-        <v>23900</v>
+        <v>18500</v>
       </c>
       <c r="Q529" t="n">
-        <v>23900</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>TO-038</t>
+          <t>TO-041</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>COJIN ANIMAL 30CM DXS-25</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24725,64 +24725,18 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N530" t="n">
-        <v>14800</v>
+        <v>2372.36</v>
       </c>
       <c r="O530" t="n">
-        <v>14800</v>
+        <v>21351.24</v>
       </c>
       <c r="P530" t="n">
-        <v>18500</v>
+        <v>41500</v>
       </c>
       <c r="Q530" t="n">
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>TO-041</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J531" t="n">
-        <v>9</v>
-      </c>
-      <c r="K531" t="n">
-        <v>0</v>
-      </c>
-      <c r="L531" t="n">
-        <v>0</v>
-      </c>
-      <c r="M531" t="n">
-        <v>9</v>
-      </c>
-      <c r="N531" t="n">
-        <v>2372.36</v>
-      </c>
-      <c r="O531" t="n">
-        <v>21351.24</v>
-      </c>
-      <c r="P531" t="n">
-        <v>41500</v>
-      </c>
-      <c r="Q531" t="n">
         <v>373500</v>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.45166808</v>
+        <v>10771715.45393164</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5654585153</v>
+        <v>1592.5654545455</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.8661135398</v>
+        <v>264365.865454553</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4721824496</v>
+        <v>35654.4725507624</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>72</v>
       </c>
       <c r="N111" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O111" t="n">
-        <v>113715.76608</v>
+        <v>113715.7000851096</v>
       </c>
       <c r="P111" t="n">
         <v>2900</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O129" t="n">
-        <v>4059.7481699346</v>
+        <v>4059.748183306</v>
       </c>
       <c r="P129" t="n">
         <v>3600</v>
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3907698744</v>
+        <v>836853.3904901209</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.3861485332</v>
+        <v>479602.390122786</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9162,10 +9162,10 @@
         <v>192</v>
       </c>
       <c r="N198" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O198" t="n">
-        <v>394767.8040670464</v>
+        <v>394767.7963309633</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9436,10 +9436,10 @@
         <v>48</v>
       </c>
       <c r="N204" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O204" t="n">
-        <v>122255.142382272</v>
+        <v>122255.12601156</v>
       </c>
       <c r="P204" t="n">
         <v>3900</v>
@@ -14870,10 +14870,10 @@
         <v>1000</v>
       </c>
       <c r="N318" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O318" t="n">
-        <v>1783798.8736264</v>
+        <v>1783798.8731104</v>
       </c>
       <c r="P318" t="n">
         <v>1500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2354586455</v>
+        <v>162931.235462754</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.116551574</v>
+        <v>2360181.109798485</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1352</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.343678303</v>
+        <v>7057447.333154577</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -4010,10 +4010,10 @@
         <v>10</v>
       </c>
       <c r="N83" t="n">
-        <v>8012</v>
+        <v>8051.1465798046</v>
       </c>
       <c r="O83" t="n">
-        <v>80120</v>
+        <v>80511.465798046</v>
       </c>
       <c r="P83" t="n">
         <v>13200</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.0602282487</v>
+        <v>923723.0589721611</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4105,10 +4105,10 @@
         <v>273</v>
       </c>
       <c r="N85" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O85" t="n">
-        <v>4046509.420000047</v>
+        <v>4051456.253031915</v>
       </c>
       <c r="P85" t="n">
         <v>24900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5653777778</v>
+        <v>1592.5653736655</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.8527111148</v>
+        <v>264365.852028473</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -5006,10 +5006,10 @@
         <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O105" t="n">
-        <v>49515</v>
+        <v>49592.3671875</v>
       </c>
       <c r="P105" t="n">
         <v>15900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.867662909</v>
+        <v>1037267.873076287</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4737474179</v>
+        <v>35654.4739622402</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O129" t="n">
-        <v>4059.7481967214</v>
+        <v>4059.7482101806</v>
       </c>
       <c r="P129" t="n">
         <v>3600</v>
@@ -6439,10 +6439,10 @@
         <v>4</v>
       </c>
       <c r="N138" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O138" t="n">
-        <v>46248.153672316</v>
+        <v>46643.437037036</v>
       </c>
       <c r="P138" t="n">
         <v>18500</v>
@@ -6954,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O150" t="n">
-        <v>39849.750846805</v>
+        <v>39941.995640432</v>
       </c>
       <c r="P150" t="n">
         <v>12900</v>
@@ -7914,10 +7914,10 @@
         <v>30</v>
       </c>
       <c r="N171" t="n">
-        <v>25749.15</v>
+        <v>24523</v>
       </c>
       <c r="O171" t="n">
-        <v>772474.5</v>
+        <v>735690</v>
       </c>
       <c r="P171" t="n">
         <v>41900</v>
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3880325616</v>
+        <v>836853.3875389632</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -8840,10 +8840,10 @@
         <v>312</v>
       </c>
       <c r="N191" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O191" t="n">
-        <v>767055.9361187735</v>
+        <v>780300.0665611632</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -8886,10 +8886,10 @@
         <v>144</v>
       </c>
       <c r="N192" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O192" t="n">
-        <v>255036.873431088</v>
+        <v>264339.1302127632</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8932,10 +8932,10 @@
         <v>216</v>
       </c>
       <c r="N193" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O193" t="n">
-        <v>449146.7983838376</v>
+        <v>449146.7973043775</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.4184633304</v>
+        <v>488752.2261287848</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9024,10 +9024,10 @@
         <v>36</v>
       </c>
       <c r="N195" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O195" t="n">
-        <v>119037.3993808056</v>
+        <v>131225.5290102372</v>
       </c>
       <c r="P195" t="n">
         <v>4900</v>
@@ -9162,10 +9162,10 @@
         <v>192</v>
       </c>
       <c r="N198" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O198" t="n">
-        <v>394767.7918738176</v>
+        <v>402014.0075563968</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9254,10 +9254,10 @@
         <v>233</v>
       </c>
       <c r="N200" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O200" t="n">
-        <v>385831.5824886507</v>
+        <v>408055.48164</v>
       </c>
       <c r="P200" t="n">
         <v>2500</v>
@@ -9300,10 +9300,10 @@
         <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="O201" t="n">
-        <v>1592.2824611033</v>
+        <v>1592.2825142045</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9390,10 +9390,10 @@
         <v>2</v>
       </c>
       <c r="N203" t="n">
-        <v>1906.1764864865</v>
+        <v>1906.1759813084</v>
       </c>
       <c r="O203" t="n">
-        <v>3812.352972973</v>
+        <v>3812.3519626168</v>
       </c>
       <c r="P203" t="n">
         <v>2900</v>
@@ -9563,22 +9563,22 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M207" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
         <v>14003</v>
       </c>
       <c r="O207" t="n">
-        <v>700150</v>
+        <v>0</v>
       </c>
       <c r="P207" t="n">
         <v>22500</v>
       </c>
       <c r="Q207" t="n">
-        <v>1125000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -10940,10 +10940,10 @@
         <v>378</v>
       </c>
       <c r="N236" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O236" t="n">
-        <v>1175896.737931041</v>
+        <v>1175896.709721733</v>
       </c>
       <c r="P236" t="n">
         <v>4500</v>
@@ -11168,10 +11168,10 @@
         <v>11930</v>
       </c>
       <c r="N241" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O241" t="n">
-        <v>8396272.092306077</v>
+        <v>8396271.860971566</v>
       </c>
       <c r="P241" t="n">
         <v>900</v>
@@ -13512,10 +13512,10 @@
         <v>4</v>
       </c>
       <c r="N290" t="n">
-        <v>18165.666666667</v>
+        <v>10899.4</v>
       </c>
       <c r="O290" t="n">
-        <v>72662.666666668</v>
+        <v>43597.6</v>
       </c>
       <c r="P290" t="n">
         <v>41500</v>
@@ -17856,10 +17856,10 @@
         <v>43</v>
       </c>
       <c r="N380" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O380" t="n">
-        <v>75564.7866825793</v>
+        <v>75564.78674641279</v>
       </c>
       <c r="P380" t="n">
         <v>2000</v>
@@ -19327,10 +19327,10 @@
         <v>72</v>
       </c>
       <c r="N412" t="n">
-        <v>7920</v>
+        <v>7945.2229299363</v>
       </c>
       <c r="O412" t="n">
-        <v>570240</v>
+        <v>572056.0509554136</v>
       </c>
       <c r="P412" t="n">
         <v>10500</v>
@@ -19376,10 +19376,10 @@
         <v>82</v>
       </c>
       <c r="N413" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="O413" t="n">
-        <v>649440</v>
+        <v>651080</v>
       </c>
       <c r="P413" t="n">
         <v>10500</v>
@@ -19425,10 +19425,10 @@
         <v>62</v>
       </c>
       <c r="N414" t="n">
-        <v>7920</v>
+        <v>8024.2105263158</v>
       </c>
       <c r="O414" t="n">
-        <v>491040</v>
+        <v>497501.0526315796</v>
       </c>
       <c r="P414" t="n">
         <v>10500</v>
@@ -19474,10 +19474,10 @@
         <v>72</v>
       </c>
       <c r="N415" t="n">
-        <v>7920</v>
+        <v>7961.0362694301</v>
       </c>
       <c r="O415" t="n">
-        <v>570240</v>
+        <v>573194.6113989672</v>
       </c>
       <c r="P415" t="n">
         <v>10500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -2379,10 +2379,10 @@
         <v>111</v>
       </c>
       <c r="N47" t="n">
-        <v>544.6367953668</v>
+        <v>538.40061776062</v>
       </c>
       <c r="O47" t="n">
-        <v>60454.6842857148</v>
+        <v>59762.46857142882</v>
       </c>
       <c r="P47" t="n">
         <v>6800</v>
@@ -2646,10 +2646,10 @@
         <v>10</v>
       </c>
       <c r="N53" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O53" t="n">
-        <v>26591.657943925</v>
+        <v>25633.4</v>
       </c>
       <c r="P53" t="n">
         <v>4700</v>
@@ -3052,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="O62" t="n">
-        <v>10897.588251121</v>
+        <v>10752.93</v>
       </c>
       <c r="P62" t="n">
         <v>18400</v>
@@ -3400,10 +3400,10 @@
         <v>11</v>
       </c>
       <c r="N70" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O70" t="n">
-        <v>189893.081922456</v>
+        <v>189281.51</v>
       </c>
       <c r="P70" t="n">
         <v>20000</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.0513978573</v>
+        <v>923723.0475862131</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4329,10 +4329,10 @@
         <v>4</v>
       </c>
       <c r="N90" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O90" t="n">
-        <v>10875.367257384</v>
+        <v>10784.36</v>
       </c>
       <c r="P90" t="n">
         <v>8200</v>
@@ -6270,10 +6270,10 @@
         <v>10</v>
       </c>
       <c r="N134" t="n">
-        <v>4355.2256097561</v>
+        <v>4355.2256790123</v>
       </c>
       <c r="O134" t="n">
-        <v>43552.256097561</v>
+        <v>43552.256790123</v>
       </c>
       <c r="P134" t="n">
         <v>7900</v>
@@ -6954,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O150" t="n">
-        <v>39941.995640432</v>
+        <v>39849.7508487655</v>
       </c>
       <c r="P150" t="n">
         <v>12900</v>
@@ -7264,10 +7264,10 @@
         <v>11</v>
       </c>
       <c r="N157" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O157" t="n">
-        <v>29125.9767167919</v>
+        <v>28980.71</v>
       </c>
       <c r="P157" t="n">
         <v>4200</v>
@@ -7448,10 +7448,10 @@
         <v>31</v>
       </c>
       <c r="N161" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O161" t="n">
-        <v>77837.5985185179</v>
+        <v>77375.38</v>
       </c>
       <c r="P161" t="n">
         <v>4100</v>
@@ -7868,10 +7868,10 @@
         <v>5</v>
       </c>
       <c r="N170" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O170" t="n">
-        <v>46895.48413793099</v>
+        <v>45944.89999999999</v>
       </c>
       <c r="P170" t="n">
         <v>12900</v>
@@ -8242,10 +8242,10 @@
         <v>382</v>
       </c>
       <c r="N178" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O178" t="n">
-        <v>2918201.647552437</v>
+        <v>2916570</v>
       </c>
       <c r="P178" t="n">
         <v>13900</v>
@@ -9662,10 +9662,10 @@
         <v>2828</v>
       </c>
       <c r="N209" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O209" t="n">
-        <v>5530953.792812801</v>
+        <v>5529410.555659587</v>
       </c>
       <c r="P209" t="n">
         <v>3000</v>
@@ -9708,10 +9708,10 @@
         <v>2640</v>
       </c>
       <c r="N210" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O210" t="n">
-        <v>3130550.772932352</v>
+        <v>3129243.653132784</v>
       </c>
       <c r="P210" t="n">
         <v>1900</v>
@@ -10042,10 +10042,10 @@
         <v>324</v>
       </c>
       <c r="N217" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O217" t="n">
-        <v>498298.475715444</v>
+        <v>495865.7735077836</v>
       </c>
       <c r="P217" t="n">
         <v>2600</v>
@@ -11076,10 +11076,10 @@
         <v>11930</v>
       </c>
       <c r="N239" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O239" t="n">
-        <v>8396271.624652224</v>
+        <v>8406782.840498626</v>
       </c>
       <c r="P239" t="n">
         <v>900</v>
@@ -14250,10 +14250,10 @@
         <v>18</v>
       </c>
       <c r="N305" t="n">
-        <v>5370.6369361702</v>
+        <v>5347.88</v>
       </c>
       <c r="O305" t="n">
-        <v>96671.4648510636</v>
+        <v>96261.84</v>
       </c>
       <c r="P305" t="n">
         <v>7900</v>
@@ -14299,10 +14299,10 @@
         <v>82</v>
       </c>
       <c r="N306" t="n">
-        <v>4593.1990728477</v>
+        <v>4578.04</v>
       </c>
       <c r="O306" t="n">
-        <v>376642.3239735114</v>
+        <v>375399.28</v>
       </c>
       <c r="P306" t="n">
         <v>7500</v>
@@ -15734,10 +15734,10 @@
         <v>159</v>
       </c>
       <c r="N336" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O336" t="n">
-        <v>838280.2494699609</v>
+        <v>829487.1</v>
       </c>
       <c r="P336" t="n">
         <v>20500</v>
@@ -16221,10 +16221,10 @@
         <v>16</v>
       </c>
       <c r="N346" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O346" t="n">
-        <v>121687.1925233648</v>
+        <v>119454.4</v>
       </c>
       <c r="P346" t="n">
         <v>11900</v>
@@ -17516,10 +17516,10 @@
         <v>159</v>
       </c>
       <c r="N373" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O373" t="n">
-        <v>112524.1140923076</v>
+        <v>112178.9471076924</v>
       </c>
       <c r="P373" t="n">
         <v>1500</v>
@@ -19788,10 +19788,10 @@
         <v>27</v>
       </c>
       <c r="N422" t="n">
-        <v>1494.6085714286</v>
+        <v>1482.84</v>
       </c>
       <c r="O422" t="n">
-        <v>40354.4314285722</v>
+        <v>40036.68</v>
       </c>
       <c r="P422" t="n">
         <v>6500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3052,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="O62" t="n">
-        <v>10899.560863636</v>
+        <v>10752.93</v>
       </c>
       <c r="P62" t="n">
         <v>18400</v>
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O72" t="n">
-        <v>2361368.872108745</v>
+        <v>2360181.058500235</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O75" t="n">
-        <v>10778145.37510324</v>
+        <v>10771715.46159766</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -3728,10 +3728,10 @@
         <v>30</v>
       </c>
       <c r="N77" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O77" t="n">
-        <v>98494.89780822</v>
+        <v>96901.98657534299</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -3918,10 +3918,10 @@
         <v>20</v>
       </c>
       <c r="N81" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O81" t="n">
-        <v>176400</v>
+        <v>175920</v>
       </c>
       <c r="P81" t="n">
         <v>14900</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O92" t="n">
-        <v>1385944.753178322</v>
+        <v>1385661.290330044</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4906,10 +4906,10 @@
         <v>99</v>
       </c>
       <c r="N103" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O103" t="n">
-        <v>373845.5440414497</v>
+        <v>372398.4</v>
       </c>
       <c r="P103" t="n">
         <v>6900</v>
@@ -7868,10 +7868,10 @@
         <v>5</v>
       </c>
       <c r="N170" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O170" t="n">
-        <v>46263.9618055555</v>
+        <v>45944.89999999999</v>
       </c>
       <c r="P170" t="n">
         <v>12900</v>
@@ -8840,10 +8840,10 @@
         <v>312</v>
       </c>
       <c r="N191" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O191" t="n">
-        <v>768708.4488904703</v>
+        <v>767055.8997199176</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -10134,10 +10134,10 @@
         <v>53</v>
       </c>
       <c r="N219" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O219" t="n">
-        <v>193476.6008543678</v>
+        <v>192356.08</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
@@ -10753,10 +10753,10 @@
         <v>59</v>
       </c>
       <c r="N232" t="n">
-        <v>3285.20748</v>
+        <v>3259.13444</v>
       </c>
       <c r="O232" t="n">
-        <v>193827.24132</v>
+        <v>192288.93196</v>
       </c>
       <c r="P232" t="n">
         <v>3600</v>
@@ -13426,10 +13426,10 @@
         <v>18</v>
       </c>
       <c r="N288" t="n">
-        <v>5480.6844036697</v>
+        <v>5430.86</v>
       </c>
       <c r="O288" t="n">
-        <v>98652.3192660546</v>
+        <v>97755.48</v>
       </c>
       <c r="P288" t="n">
         <v>13900</v>
@@ -14106,10 +14106,10 @@
         <v>74</v>
       </c>
       <c r="N302" t="n">
-        <v>4234.4238541667</v>
+        <v>4190.77</v>
       </c>
       <c r="O302" t="n">
-        <v>313347.3652083358</v>
+        <v>310116.98</v>
       </c>
       <c r="P302" t="n">
         <v>5900</v>
@@ -14155,10 +14155,10 @@
         <v>252</v>
       </c>
       <c r="N303" t="n">
-        <v>3503.9263942308</v>
+        <v>3499.72</v>
       </c>
       <c r="O303" t="n">
-        <v>882989.4513461615</v>
+        <v>881929.4399999999</v>
       </c>
       <c r="P303" t="n">
         <v>6900</v>
@@ -14204,10 +14204,10 @@
         <v>18</v>
       </c>
       <c r="N304" t="n">
-        <v>5370.7341880342</v>
+        <v>5347.88</v>
       </c>
       <c r="O304" t="n">
-        <v>96673.2153846156</v>
+        <v>96261.84</v>
       </c>
       <c r="P304" t="n">
         <v>7900</v>
@@ -14253,10 +14253,10 @@
         <v>82</v>
       </c>
       <c r="N305" t="n">
-        <v>4593.2494352159</v>
+        <v>4578.04</v>
       </c>
       <c r="O305" t="n">
-        <v>376646.4536877038</v>
+        <v>375399.28</v>
       </c>
       <c r="P305" t="n">
         <v>7500</v>
@@ -16273,10 +16273,10 @@
         <v>8</v>
       </c>
       <c r="N347" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O347" t="n">
-        <v>56448.6860653256</v>
+        <v>56375.5186156176</v>
       </c>
       <c r="P347" t="n">
         <v>9900</v>
@@ -21150,10 +21150,10 @@
         <v>582</v>
       </c>
       <c r="N451" t="n">
-        <v>2547.0191593353</v>
+        <v>2539.5717399804</v>
       </c>
       <c r="O451" t="n">
-        <v>1482365.150733145</v>
+        <v>1478030.752668593</v>
       </c>
       <c r="P451" t="n">
         <v>2900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1043,10 +1043,10 @@
         <v>23</v>
       </c>
       <c r="N16" t="n">
-        <v>3926.8370787689</v>
+        <v>3926.8370772443</v>
       </c>
       <c r="O16" t="n">
-        <v>90317.2528116847</v>
+        <v>90317.2527766189</v>
       </c>
       <c r="P16" t="n">
         <v>4800</v>
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101685824</v>
+        <v>4937.310172549</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2355632192</v>
+        <v>162931.235694117</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2549874182</v>
+        <v>2582.2549620637</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.058500235</v>
+        <v>2360181.035326222</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3538,19 +3538,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>1352</v>
+        <v>1338</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8959284856</v>
+        <v>5216.8958877086</v>
       </c>
       <c r="O73" t="n">
-        <v>7053243.295312531</v>
+        <v>6980206.697754106</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
       </c>
       <c r="Q73" t="n">
-        <v>11492000</v>
+        <v>11373000</v>
       </c>
     </row>
     <row r="74">
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2530785869</v>
+        <v>3594.2530181818</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.0411968332</v>
+        <v>923723.0256727226</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712628708</v>
+        <v>4371.1712629569</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.290330044</v>
+        <v>1385661.290357337</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.565202952</v>
+        <v>1592.5651537745</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.823690032</v>
+        <v>264365.815526567</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.924511587</v>
+        <v>1630.9246047904</v>
       </c>
       <c r="O109" t="n">
-        <v>1037267.989369332</v>
+        <v>1037268.048646694</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1946099379</v>
+        <v>1550.1946673374</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4760285717</v>
+        <v>35654.4773487602</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -5280,10 +5280,10 @@
         <v>72</v>
       </c>
       <c r="N111" t="n">
-        <v>1579.3838288288</v>
+        <v>1579.3828229665</v>
       </c>
       <c r="O111" t="n">
-        <v>113715.6356756736</v>
+        <v>113715.563253588</v>
       </c>
       <c r="P111" t="n">
         <v>2900</v>
@@ -6065,10 +6065,10 @@
         <v>2</v>
       </c>
       <c r="N129" t="n">
-        <v>2029.8741413584</v>
+        <v>2029.8741689828</v>
       </c>
       <c r="O129" t="n">
-        <v>4059.7482827168</v>
+        <v>4059.7483379656</v>
       </c>
       <c r="P129" t="n">
         <v>3600</v>
@@ -6147,10 +6147,10 @@
         <v>141</v>
       </c>
       <c r="N131" t="n">
-        <v>2680.7396939413</v>
+        <v>2680.7396933667</v>
       </c>
       <c r="O131" t="n">
-        <v>377984.2968457234</v>
+        <v>377984.2967647047</v>
       </c>
       <c r="P131" t="n">
         <v>4900</v>
@@ -6188,10 +6188,10 @@
         <v>402</v>
       </c>
       <c r="N132" t="n">
-        <v>880.32982103457</v>
+        <v>880.32985728346</v>
       </c>
       <c r="O132" t="n">
-        <v>353892.5880558972</v>
+        <v>353892.6026279509</v>
       </c>
       <c r="P132" t="n">
         <v>1200</v>
@@ -6954,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>7969.9501697531</v>
+        <v>7969.9501704105</v>
       </c>
       <c r="O150" t="n">
-        <v>39849.7508487655</v>
+        <v>39849.7508520525</v>
       </c>
       <c r="P150" t="n">
         <v>12900</v>
@@ -8564,10 +8564,10 @@
         <v>344</v>
       </c>
       <c r="N185" t="n">
-        <v>17075.989518828</v>
+        <v>17075.989518156</v>
       </c>
       <c r="O185" t="n">
-        <v>5874140.394476832</v>
+        <v>5874140.394245664</v>
       </c>
       <c r="P185" t="n">
         <v>27500</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8699,19 +8699,19 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N188" t="n">
         <v>10713.21</v>
       </c>
       <c r="O188" t="n">
-        <v>910622.85</v>
+        <v>835630.3799999999</v>
       </c>
       <c r="P188" t="n">
         <v>20900</v>
       </c>
       <c r="Q188" t="n">
-        <v>1776500</v>
+        <v>1630200</v>
       </c>
     </row>
     <row r="189">
@@ -8794,10 +8794,10 @@
         <v>552</v>
       </c>
       <c r="N190" t="n">
-        <v>1516.0387397625</v>
+        <v>1516.0387386003</v>
       </c>
       <c r="O190" t="n">
-        <v>836853.3843488999</v>
+        <v>836853.3837073655</v>
       </c>
       <c r="P190" t="n">
         <v>2300</v>
@@ -8840,10 +8840,10 @@
         <v>312</v>
       </c>
       <c r="N191" t="n">
-        <v>2458.5124991023</v>
+        <v>2458.5124311594</v>
       </c>
       <c r="O191" t="n">
-        <v>767055.8997199176</v>
+        <v>767055.8785217328</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -8886,10 +8886,10 @@
         <v>144</v>
       </c>
       <c r="N192" t="n">
-        <v>1771.0893598234</v>
+        <v>1771.0893441415</v>
       </c>
       <c r="O192" t="n">
-        <v>255036.8678145696</v>
+        <v>255036.865556376</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8932,10 +8932,10 @@
         <v>216</v>
       </c>
       <c r="N193" t="n">
-        <v>2079.3833133433</v>
+        <v>2079.3832881866</v>
       </c>
       <c r="O193" t="n">
-        <v>449146.7956821528</v>
+        <v>449146.7902483057</v>
       </c>
       <c r="P193" t="n">
         <v>2900</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0169552729</v>
+        <v>1803.0169781803</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.5101025914</v>
+        <v>479602.5161959598</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>72</v>
       </c>
       <c r="N197" t="n">
-        <v>2108.7969844358</v>
+        <v>2108.7971008815</v>
       </c>
       <c r="O197" t="n">
-        <v>151833.3828793776</v>
+        <v>151833.391263468</v>
       </c>
       <c r="P197" t="n">
         <v>2900</v>
@@ -9162,10 +9162,10 @@
         <v>192</v>
       </c>
       <c r="N198" t="n">
-        <v>2056.0821161192</v>
+        <v>2056.0820030996</v>
       </c>
       <c r="O198" t="n">
-        <v>394767.7662948864</v>
+        <v>394767.7445951232</v>
       </c>
       <c r="P198" t="n">
         <v>2900</v>
@@ -9208,10 +9208,10 @@
         <v>162</v>
       </c>
       <c r="N199" t="n">
-        <v>3224.5697707424</v>
+        <v>3224.5698459846</v>
       </c>
       <c r="O199" t="n">
-        <v>522380.3028602688</v>
+        <v>522380.3150495052</v>
       </c>
       <c r="P199" t="n">
         <v>4500</v>
@@ -9254,10 +9254,10 @@
         <v>233</v>
       </c>
       <c r="N200" t="n">
-        <v>1655.9292163743</v>
+        <v>1655.9292037471</v>
       </c>
       <c r="O200" t="n">
-        <v>385831.5074152119</v>
+        <v>385831.5044730743</v>
       </c>
       <c r="P200" t="n">
         <v>2500</v>
@@ -9300,10 +9300,10 @@
         <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>1592.2831886228</v>
+        <v>1592.2838740157</v>
       </c>
       <c r="O201" t="n">
-        <v>1592.2831886228</v>
+        <v>1592.2838740157</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9390,10 +9390,10 @@
         <v>600</v>
       </c>
       <c r="N203" t="n">
-        <v>1259.274867406</v>
+        <v>1259.2749291992</v>
       </c>
       <c r="O203" t="n">
-        <v>755564.9204436</v>
+        <v>755564.95751952</v>
       </c>
       <c r="P203" t="n">
         <v>1900</v>
@@ -9521,10 +9521,10 @@
         <v>192</v>
       </c>
       <c r="N206" t="n">
-        <v>692.1524140338601</v>
+        <v>692.15241910093</v>
       </c>
       <c r="O206" t="n">
-        <v>132893.2634945011</v>
+        <v>132893.2644673786</v>
       </c>
       <c r="P206" t="n">
         <v>1200</v>
@@ -9996,10 +9996,10 @@
         <v>324</v>
       </c>
       <c r="N216" t="n">
-        <v>1530.4499182339</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O216" t="n">
-        <v>495865.7735077836</v>
+        <v>495865.7734535136</v>
       </c>
       <c r="P216" t="n">
         <v>2600</v>
@@ -10367,10 +10367,10 @@
         <v>1</v>
       </c>
       <c r="N224" t="n">
-        <v>1690.8700093809</v>
+        <v>1690.8700094029</v>
       </c>
       <c r="O224" t="n">
-        <v>1690.8700093809</v>
+        <v>1690.8700094029</v>
       </c>
       <c r="P224" t="n">
         <v>3000</v>
@@ -10753,10 +10753,10 @@
         <v>59</v>
       </c>
       <c r="N232" t="n">
-        <v>3259.13444</v>
+        <v>3259.134625</v>
       </c>
       <c r="O232" t="n">
-        <v>192288.93196</v>
+        <v>192288.942875</v>
       </c>
       <c r="P232" t="n">
         <v>3600</v>
@@ -10802,10 +10802,10 @@
         <v>378</v>
       </c>
       <c r="N233" t="n">
-        <v>3110.837275018</v>
+        <v>3110.8368831169</v>
       </c>
       <c r="O233" t="n">
-        <v>1175896.489956804</v>
+        <v>1175896.341818188</v>
       </c>
       <c r="P233" t="n">
         <v>4500</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>11930</v>
+        <v>11642</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -11027,19 +11027,19 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>11930</v>
+        <v>11642</v>
       </c>
       <c r="N238" t="n">
-        <v>703.7947515264</v>
+        <v>703.7947376286299</v>
       </c>
       <c r="O238" t="n">
-        <v>8396271.385709953</v>
+        <v>8193578.33547251</v>
       </c>
       <c r="P238" t="n">
         <v>900</v>
       </c>
       <c r="Q238" t="n">
-        <v>10737000</v>
+        <v>10477800</v>
       </c>
     </row>
     <row r="239">
@@ -11125,10 +11125,10 @@
         <v>161</v>
       </c>
       <c r="N240" t="n">
-        <v>3182.2511299435</v>
+        <v>3182.2511320755</v>
       </c>
       <c r="O240" t="n">
-        <v>512342.4319209035</v>
+        <v>512342.4322641555</v>
       </c>
       <c r="P240" t="n">
         <v>6900</v>
@@ -11309,10 +11309,10 @@
         <v>59</v>
       </c>
       <c r="N244" t="n">
-        <v>2501.3844329897</v>
+        <v>2501.3844041451</v>
       </c>
       <c r="O244" t="n">
-        <v>147581.6815463923</v>
+        <v>147581.6798445609</v>
       </c>
       <c r="P244" t="n">
         <v>4100</v>
@@ -11502,10 +11502,10 @@
         <v>62</v>
       </c>
       <c r="N248" t="n">
-        <v>6078.9925962596</v>
+        <v>6078.9926048565</v>
       </c>
       <c r="O248" t="n">
-        <v>376897.5409680952</v>
+        <v>376897.541501103</v>
       </c>
       <c r="P248" t="n">
         <v>18500</v>
@@ -13463,7 +13463,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -13472,19 +13472,19 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N289" t="n">
         <v>5697.97</v>
       </c>
       <c r="O289" t="n">
-        <v>501421.36</v>
+        <v>490025.42</v>
       </c>
       <c r="P289" t="n">
         <v>19500</v>
       </c>
       <c r="Q289" t="n">
-        <v>1716000</v>
+        <v>1677000</v>
       </c>
     </row>
     <row r="290">
@@ -14444,10 +14444,10 @@
         <v>1000</v>
       </c>
       <c r="N309" t="n">
-        <v>1783.7988731104</v>
+        <v>1783.7988700046</v>
       </c>
       <c r="O309" t="n">
-        <v>1783798.8731104</v>
+        <v>1783798.8700046</v>
       </c>
       <c r="P309" t="n">
         <v>1500</v>
@@ -16273,10 +16273,10 @@
         <v>8</v>
       </c>
       <c r="N347" t="n">
-        <v>7046.9398269522</v>
+        <v>7046.9398267273</v>
       </c>
       <c r="O347" t="n">
-        <v>56375.5186156176</v>
+        <v>56375.5186138184</v>
       </c>
       <c r="P347" t="n">
         <v>9900</v>
@@ -17005,10 +17005,10 @@
         <v>984</v>
       </c>
       <c r="N362" t="n">
-        <v>430.60997550521</v>
+        <v>430.60997530864</v>
       </c>
       <c r="O362" t="n">
-        <v>423720.2158971266</v>
+        <v>423720.2157037018</v>
       </c>
       <c r="P362" t="n">
         <v>2200</v>
@@ -17054,10 +17054,10 @@
         <v>726</v>
       </c>
       <c r="N363" t="n">
-        <v>465.871</v>
+        <v>465.87102642276</v>
       </c>
       <c r="O363" t="n">
-        <v>338222.346</v>
+        <v>338222.3651829237</v>
       </c>
       <c r="P363" t="n">
         <v>2500</v>
@@ -18270,10 +18270,10 @@
         <v>1527</v>
       </c>
       <c r="N389" t="n">
-        <v>220.00190038478</v>
+        <v>220.00066011878</v>
       </c>
       <c r="O389" t="n">
-        <v>335942.901887559</v>
+        <v>335941.008001377</v>
       </c>
       <c r="P389" t="n">
         <v>260</v>
@@ -18858,10 +18858,10 @@
         <v>3</v>
       </c>
       <c r="N402" t="n">
-        <v>9855.0380769231</v>
+        <v>9855.038</v>
       </c>
       <c r="O402" t="n">
-        <v>29565.1142307693</v>
+        <v>29565.114</v>
       </c>
       <c r="P402" t="n">
         <v>15500</v>
@@ -19275,7 +19275,7 @@
         </is>
       </c>
       <c r="J411" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="K411" t="n">
         <v>0</v>
@@ -19284,19 +19284,19 @@
         <v>0</v>
       </c>
       <c r="M411" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="N411" t="n">
         <v>9240</v>
       </c>
       <c r="O411" t="n">
-        <v>5544000</v>
+        <v>4989600</v>
       </c>
       <c r="P411" t="n">
         <v>11500</v>
       </c>
       <c r="Q411" t="n">
-        <v>6900000</v>
+        <v>6210000</v>
       </c>
     </row>
     <row r="412">
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="J430" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K430" t="n">
         <v>0</v>
@@ -20158,19 +20158,19 @@
         <v>0</v>
       </c>
       <c r="M430" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N430" t="n">
         <v>9046.99</v>
       </c>
       <c r="O430" t="n">
-        <v>63328.93</v>
+        <v>54281.94</v>
       </c>
       <c r="P430" t="n">
         <v>22500</v>
       </c>
       <c r="Q430" t="n">
-        <v>157500</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="431">
@@ -20207,10 +20207,10 @@
         <v>18</v>
       </c>
       <c r="N431" t="n">
-        <v>1319.3609646302</v>
+        <v>1319.3609677419</v>
       </c>
       <c r="O431" t="n">
-        <v>23748.4973633436</v>
+        <v>23748.4974193542</v>
       </c>
       <c r="P431" t="n">
         <v>3500</v>
@@ -20304,10 +20304,10 @@
         <v>36</v>
       </c>
       <c r="N433" t="n">
-        <v>3088.1452173913</v>
+        <v>3088.1459090909</v>
       </c>
       <c r="O433" t="n">
-        <v>111173.2278260868</v>
+        <v>111173.2527272724</v>
       </c>
       <c r="P433" t="n">
         <v>8500</v>
@@ -21150,10 +21150,10 @@
         <v>582</v>
       </c>
       <c r="N451" t="n">
-        <v>2539.5717399804</v>
+        <v>2539.5717536946</v>
       </c>
       <c r="O451" t="n">
-        <v>1478030.752668593</v>
+        <v>1478030.760650257</v>
       </c>
       <c r="P451" t="n">
         <v>2900</v>
@@ -21196,10 +21196,10 @@
         <v>561</v>
       </c>
       <c r="N452" t="n">
-        <v>4687.9748390244</v>
+        <v>4687.974964965</v>
       </c>
       <c r="O452" t="n">
-        <v>2629953.884692688</v>
+        <v>2629953.955345365</v>
       </c>
       <c r="P452" t="n">
         <v>5500</v>
@@ -21242,10 +21242,10 @@
         <v>80</v>
       </c>
       <c r="N453" t="n">
-        <v>4171.6685076531</v>
+        <v>4171.6685019206</v>
       </c>
       <c r="O453" t="n">
-        <v>333733.480612248</v>
+        <v>333733.4801536479</v>
       </c>
       <c r="P453" t="n">
         <v>5000</v>
@@ -21569,10 +21569,10 @@
         <v>24</v>
       </c>
       <c r="N460" t="n">
-        <v>2361.5097058824</v>
+        <v>2361.5096875</v>
       </c>
       <c r="O460" t="n">
-        <v>56676.2329411776</v>
+        <v>56676.2325</v>
       </c>
       <c r="P460" t="n">
         <v>6200</v>
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -21612,19 +21612,19 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N461" t="n">
-        <v>7046.7392307692</v>
+        <v>7046.74</v>
       </c>
       <c r="O461" t="n">
-        <v>169121.7415384608</v>
+        <v>133888.06</v>
       </c>
       <c r="P461" t="n">
         <v>22900</v>
       </c>
       <c r="Q461" t="n">
-        <v>549600</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="462">
@@ -21661,10 +21661,10 @@
         <v>3</v>
       </c>
       <c r="N462" t="n">
-        <v>10009.172222222</v>
+        <v>10009.1725</v>
       </c>
       <c r="O462" t="n">
-        <v>30027.516666666</v>
+        <v>30027.5175</v>
       </c>
       <c r="P462" t="n">
         <v>22900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -920,22 +920,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N13" t="n">
         <v>27000</v>
       </c>
       <c r="O13" t="n">
-        <v>2673000</v>
+        <v>2592000</v>
       </c>
       <c r="P13" t="n">
         <v>20000</v>
       </c>
       <c r="Q13" t="n">
-        <v>1980000</v>
+        <v>1920000</v>
       </c>
     </row>
     <row r="14">
@@ -3495,10 +3495,10 @@
         <v>914</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O72" t="n">
-        <v>2360181.035326222</v>
+        <v>2360181.034161421</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1338</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O73" t="n">
-        <v>6980206.697754106</v>
+        <v>6980206.695248167</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.46159766</v>
+        <v>10771715.4617402</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -4059,10 +4059,10 @@
         <v>257</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O84" t="n">
-        <v>923723.0256727226</v>
+        <v>923723.0204376326</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.290357337</v>
+        <v>1385850.30431046</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -4636,10 +4636,10 @@
         <v>152</v>
       </c>
       <c r="N97" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O97" t="n">
-        <v>555705.92</v>
+        <v>557578.6651808536</v>
       </c>
       <c r="P97" t="n">
         <v>5500</v>
@@ -5188,10 +5188,10 @@
         <v>636</v>
       </c>
       <c r="N109" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O109" t="n">
-        <v>1037268.048646694</v>
+        <v>1037268.050401418</v>
       </c>
       <c r="P109" t="n">
         <v>2500</v>
@@ -5234,10 +5234,10 @@
         <v>23</v>
       </c>
       <c r="N110" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O110" t="n">
-        <v>35654.4773487602</v>
+        <v>35681.4339805955</v>
       </c>
       <c r="P110" t="n">
         <v>2500</v>
@@ -6954,10 +6954,10 @@
         <v>5</v>
       </c>
       <c r="N150" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O150" t="n">
-        <v>39849.7508520525</v>
+        <v>39849.7508533745</v>
       </c>
       <c r="P150" t="n">
         <v>12900</v>
@@ -8840,10 +8840,10 @@
         <v>312</v>
       </c>
       <c r="N191" t="n">
-        <v>2458.5124311594</v>
+        <v>2458.5124201742</v>
       </c>
       <c r="O191" t="n">
-        <v>767055.8785217328</v>
+        <v>767055.8750943504</v>
       </c>
       <c r="P191" t="n">
         <v>3500</v>
@@ -8886,10 +8886,10 @@
         <v>144</v>
       </c>
       <c r="N192" t="n">
-        <v>1771.0893441415</v>
+        <v>1771.0893205318</v>
       </c>
       <c r="O192" t="n">
-        <v>255036.865556376</v>
+        <v>255036.8621565792</v>
       </c>
       <c r="P192" t="n">
         <v>2500</v>
@@ -8978,10 +8978,10 @@
         <v>266</v>
       </c>
       <c r="N194" t="n">
-        <v>1803.0169781803</v>
+        <v>1803.0169868096</v>
       </c>
       <c r="O194" t="n">
-        <v>479602.5161959598</v>
+        <v>479602.5184913536</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9300,10 +9300,10 @@
         <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>1592.2838740157</v>
+        <v>1592.2847324415</v>
       </c>
       <c r="O201" t="n">
-        <v>1592.2838740157</v>
+        <v>1592.2847324415</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>
@@ -9390,10 +9390,10 @@
         <v>600</v>
       </c>
       <c r="N203" t="n">
-        <v>1259.2749291992</v>
+        <v>1262.9750514202</v>
       </c>
       <c r="O203" t="n">
-        <v>755564.95751952</v>
+        <v>757785.03085212</v>
       </c>
       <c r="P203" t="n">
         <v>1900</v>
@@ -9996,10 +9996,10 @@
         <v>324</v>
       </c>
       <c r="N216" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O216" t="n">
-        <v>495865.7734535136</v>
+        <v>498315.5014409136</v>
       </c>
       <c r="P216" t="n">
         <v>2600</v>
@@ -10802,10 +10802,10 @@
         <v>378</v>
       </c>
       <c r="N233" t="n">
-        <v>3110.8368831169</v>
+        <v>3110.8366754617</v>
       </c>
       <c r="O233" t="n">
-        <v>1175896.341818188</v>
+        <v>1175896.263324523</v>
       </c>
       <c r="P233" t="n">
         <v>4500</v>
@@ -11030,10 +11030,10 @@
         <v>11642</v>
       </c>
       <c r="N238" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O238" t="n">
-        <v>8193578.33547251</v>
+        <v>8193578.29689942</v>
       </c>
       <c r="P238" t="n">
         <v>900</v>
@@ -11885,22 +11885,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M256" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
         <v>12857.91</v>
       </c>
       <c r="O256" t="n">
-        <v>25715.82</v>
+        <v>0</v>
       </c>
       <c r="P256" t="n">
         <v>21500</v>
       </c>
       <c r="Q256" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -14735,10 +14735,10 @@
         <v>1</v>
       </c>
       <c r="N315" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="O315" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="P315" t="n">
         <v>18900</v>
@@ -17005,10 +17005,10 @@
         <v>984</v>
       </c>
       <c r="N362" t="n">
-        <v>430.60997530864</v>
+        <v>430.60997520149</v>
       </c>
       <c r="O362" t="n">
-        <v>423720.2157037018</v>
+        <v>423720.2155982662</v>
       </c>
       <c r="P362" t="n">
         <v>2200</v>
@@ -18996,10 +18996,10 @@
         <v>288</v>
       </c>
       <c r="N405" t="n">
-        <v>6160</v>
+        <v>6202.5414364641</v>
       </c>
       <c r="O405" t="n">
-        <v>1774080</v>
+        <v>1786331.933701661</v>
       </c>
       <c r="P405" t="n">
         <v>7500</v>
@@ -21196,10 +21196,10 @@
         <v>561</v>
       </c>
       <c r="N452" t="n">
-        <v>4687.974964965</v>
+        <v>4687.9750151668</v>
       </c>
       <c r="O452" t="n">
-        <v>2629953.955345365</v>
+        <v>2629953.983508575</v>
       </c>
       <c r="P452" t="n">
         <v>5500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -9300,10 +9300,10 @@
         <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="O201" t="n">
-        <v>1592.2857321429</v>
+        <v>1592.2857602862</v>
       </c>
       <c r="P201" t="n">
         <v>2500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -4059,10 +4059,10 @@
         <v>233</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O84" t="n">
-        <v>837460.9328718798</v>
+        <v>837460.9316580663</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -5137,10 +5137,10 @@
         <v>636</v>
       </c>
       <c r="N108" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O108" t="n">
-        <v>1037268.096774214</v>
+        <v>1037268.107684794</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -8743,10 +8743,10 @@
         <v>552</v>
       </c>
       <c r="N189" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O189" t="n">
-        <v>836853.3820624609</v>
+        <v>836853.3794721457</v>
       </c>
       <c r="P189" t="n">
         <v>2300</v>
@@ -16865,10 +16865,10 @@
         <v>726</v>
       </c>
       <c r="N359" t="n">
-        <v>465.87102642276</v>
+        <v>465.87102746694</v>
       </c>
       <c r="O359" t="n">
-        <v>338222.3651829237</v>
+        <v>338222.3659409984</v>
       </c>
       <c r="P359" t="n">
         <v>2500</v>
@@ -20912,10 +20912,10 @@
         <v>582</v>
       </c>
       <c r="N446" t="n">
-        <v>2539.571774676</v>
+        <v>2539.5717817818</v>
       </c>
       <c r="O446" t="n">
-        <v>1478030.772861432</v>
+        <v>1478030.776997008</v>
       </c>
       <c r="P446" t="n">
         <v>2900</v>
@@ -21004,10 +21004,10 @@
         <v>80</v>
       </c>
       <c r="N448" t="n">
-        <v>4171.6684503311</v>
+        <v>4171.6684420772</v>
       </c>
       <c r="O448" t="n">
-        <v>333733.476026488</v>
+        <v>333733.475366176</v>
       </c>
       <c r="P448" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3728,10 +3728,10 @@
         <v>30</v>
       </c>
       <c r="N77" t="n">
-        <v>3230.0661344538</v>
+        <v>3230.0661016949</v>
       </c>
       <c r="O77" t="n">
-        <v>96901.98403361399</v>
+        <v>96901.983050847</v>
       </c>
       <c r="P77" t="n">
         <v>6200</v>
@@ -3863,22 +3863,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N80" t="n">
         <v>9664</v>
       </c>
       <c r="O80" t="n">
-        <v>96640</v>
+        <v>86976</v>
       </c>
       <c r="P80" t="n">
         <v>15900</v>
       </c>
       <c r="Q80" t="n">
-        <v>159000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="81">
@@ -4416,10 +4416,10 @@
         <v>317</v>
       </c>
       <c r="N92" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O92" t="n">
-        <v>1385661.290493901</v>
+        <v>1385661.290657885</v>
       </c>
       <c r="P92" t="n">
         <v>8900</v>
@@ -5137,10 +5137,10 @@
         <v>636</v>
       </c>
       <c r="N108" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O108" t="n">
-        <v>1037268.108597644</v>
+        <v>1037268.112254517</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -8702,10 +8702,10 @@
         <v>552</v>
       </c>
       <c r="N188" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O188" t="n">
-        <v>836853.3774441528</v>
+        <v>836853.3772988664</v>
       </c>
       <c r="P188" t="n">
         <v>2300</v>
@@ -8794,10 +8794,10 @@
         <v>144</v>
       </c>
       <c r="N190" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O190" t="n">
-        <v>255036.8621565792</v>
+        <v>255036.834406008</v>
       </c>
       <c r="P190" t="n">
         <v>2500</v>
@@ -9116,10 +9116,10 @@
         <v>162</v>
       </c>
       <c r="N197" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O197" t="n">
-        <v>522380.3274279414</v>
+        <v>522380.3292119826</v>
       </c>
       <c r="P197" t="n">
         <v>4500</v>
@@ -9162,10 +9162,10 @@
         <v>233</v>
       </c>
       <c r="N198" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O198" t="n">
-        <v>385831.4846813553</v>
+        <v>385831.4605162729</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -10710,10 +10710,10 @@
         <v>378</v>
       </c>
       <c r="N231" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O231" t="n">
-        <v>1175895.995394985</v>
+        <v>1175895.982729793</v>
       </c>
       <c r="P231" t="n">
         <v>4500</v>
@@ -10938,10 +10938,10 @@
         <v>11354</v>
       </c>
       <c r="N236" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O236" t="n">
-        <v>7990884.978961238</v>
+        <v>7990884.849788028</v>
       </c>
       <c r="P236" t="n">
         <v>900</v>
@@ -12090,10 +12090,10 @@
         <v>5</v>
       </c>
       <c r="N260" t="n">
-        <v>2832.1953125</v>
+        <v>2832.1953968254</v>
       </c>
       <c r="O260" t="n">
-        <v>14160.9765625</v>
+        <v>14160.976984127</v>
       </c>
       <c r="P260" t="n">
         <v>12900</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -1199,10 +1199,10 @@
         <v>23</v>
       </c>
       <c r="N20" t="n">
-        <v>2785.6243902439</v>
+        <v>2681</v>
       </c>
       <c r="O20" t="n">
-        <v>64069.3609756097</v>
+        <v>61663</v>
       </c>
       <c r="P20" t="n">
         <v>3500</v>
@@ -2916,10 +2916,10 @@
         <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>1367.2464516129</v>
+        <v>1324.52</v>
       </c>
       <c r="O59" t="n">
-        <v>4101.7393548387</v>
+        <v>3973.56</v>
       </c>
       <c r="P59" t="n">
         <v>20500</v>
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101733649</v>
+        <v>4937.3101737757</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2357210417</v>
+        <v>162931.2357345981</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2548633316</v>
+        <v>2582.2548540429</v>
       </c>
       <c r="O72" t="n">
-        <v>2329193.886725103</v>
+        <v>2329193.878346696</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -4059,10 +4059,10 @@
         <v>233</v>
       </c>
       <c r="N84" t="n">
-        <v>3594.2528730512</v>
+        <v>3594.2528624535</v>
       </c>
       <c r="O84" t="n">
-        <v>837460.9194209296</v>
+        <v>837460.9169516654</v>
       </c>
       <c r="P84" t="n">
         <v>6500</v>
@@ -4149,10 +4149,10 @@
         <v>192</v>
       </c>
       <c r="N86" t="n">
-        <v>2093.3158067369</v>
+        <v>2090.85</v>
       </c>
       <c r="O86" t="n">
-        <v>401916.6348934848</v>
+        <v>401443.2</v>
       </c>
       <c r="P86" t="n">
         <v>2900</v>
@@ -4549,10 +4549,10 @@
         <v>166</v>
       </c>
       <c r="N95" t="n">
-        <v>1592.5646884576</v>
+        <v>1592.5646666667</v>
       </c>
       <c r="O95" t="n">
-        <v>264365.7382839616</v>
+        <v>264365.7346666722</v>
       </c>
       <c r="P95" t="n">
         <v>3900</v>
@@ -5137,10 +5137,10 @@
         <v>636</v>
       </c>
       <c r="N108" t="n">
-        <v>1630.9247235872</v>
+        <v>1630.9247279434</v>
       </c>
       <c r="O108" t="n">
-        <v>1037268.124201459</v>
+        <v>1037268.126972002</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -8564,10 +8564,10 @@
         <v>78</v>
       </c>
       <c r="N185" t="n">
-        <v>10795.831156812</v>
+        <v>10713.21</v>
       </c>
       <c r="O185" t="n">
-        <v>842074.8302313361</v>
+        <v>835630.3799999999</v>
       </c>
       <c r="P185" t="n">
         <v>20900</v>
@@ -8656,10 +8656,10 @@
         <v>552</v>
       </c>
       <c r="N187" t="n">
-        <v>1516.0387131507</v>
+        <v>1516.0387126124</v>
       </c>
       <c r="O187" t="n">
-        <v>836853.3696591865</v>
+        <v>836853.3693620448</v>
       </c>
       <c r="P187" t="n">
         <v>2300</v>
@@ -9162,10 +9162,10 @@
         <v>1</v>
       </c>
       <c r="N198" t="n">
-        <v>1592.2864981273</v>
+        <v>1592.2866856061</v>
       </c>
       <c r="O198" t="n">
-        <v>1592.2864981273</v>
+        <v>1592.2866856061</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
@@ -9383,10 +9383,10 @@
         <v>192</v>
       </c>
       <c r="N203" t="n">
-        <v>692.15249234096</v>
+        <v>692.15249774246</v>
       </c>
       <c r="O203" t="n">
-        <v>132893.2785294643</v>
+        <v>132893.2795665523</v>
       </c>
       <c r="P203" t="n">
         <v>1200</v>
@@ -9432,10 +9432,10 @@
         <v>3</v>
       </c>
       <c r="N204" t="n">
-        <v>19051.333333333</v>
+        <v>18491</v>
       </c>
       <c r="O204" t="n">
-        <v>57153.999999999</v>
+        <v>55473</v>
       </c>
       <c r="P204" t="n">
         <v>13500</v>
@@ -10892,10 +10892,10 @@
         <v>11066</v>
       </c>
       <c r="N235" t="n">
-        <v>703.79465893216</v>
+        <v>703.79465786602</v>
       </c>
       <c r="O235" t="n">
-        <v>7788191.695743282</v>
+        <v>7788191.683945377</v>
       </c>
       <c r="P235" t="n">
         <v>900</v>
@@ -13588,10 +13588,10 @@
         <v>60</v>
       </c>
       <c r="N291" t="n">
-        <v>3099.0394791667</v>
+        <v>3067.090625</v>
       </c>
       <c r="O291" t="n">
-        <v>185942.368750002</v>
+        <v>184025.4375</v>
       </c>
       <c r="P291" t="n">
         <v>7200</v>
@@ -13830,10 +13830,10 @@
         <v>74</v>
       </c>
       <c r="N296" t="n">
-        <v>4234.8833684211</v>
+        <v>4190.77</v>
       </c>
       <c r="O296" t="n">
-        <v>313381.3692631614</v>
+        <v>310116.98</v>
       </c>
       <c r="P296" t="n">
         <v>5900</v>
@@ -16582,10 +16582,10 @@
         <v>89</v>
       </c>
       <c r="N353" t="n">
-        <v>548.38743842365</v>
+        <v>540.40123152709</v>
       </c>
       <c r="O353" t="n">
-        <v>48806.48201970485</v>
+        <v>48095.709605911</v>
       </c>
       <c r="P353" t="n">
         <v>2500</v>
@@ -17347,10 +17347,10 @@
         <v>43</v>
       </c>
       <c r="N369" t="n">
-        <v>1757.3206341463</v>
+        <v>1757.3206356968</v>
       </c>
       <c r="O369" t="n">
-        <v>75564.78726829091</v>
+        <v>75564.7873349624</v>
       </c>
       <c r="P369" t="n">
         <v>2000</v>
@@ -19873,25 +19873,25 @@
         <v>18</v>
       </c>
       <c r="K424" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M424" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N424" t="n">
-        <v>1333.5477419355</v>
+        <v>1319.3610452962</v>
       </c>
       <c r="O424" t="n">
-        <v>24003.859354839</v>
+        <v>10554.8883623696</v>
       </c>
       <c r="P424" t="n">
         <v>3500</v>
       </c>
       <c r="Q424" t="n">
-        <v>63000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="425">
@@ -20871,10 +20871,10 @@
         <v>561</v>
       </c>
       <c r="N445" t="n">
-        <v>4687.9753161844</v>
+        <v>4687.9753276047</v>
       </c>
       <c r="O445" t="n">
-        <v>2629954.152379449</v>
+        <v>2629954.158786237</v>
       </c>
       <c r="P445" t="n">
         <v>5500</v>
@@ -21658,10 +21658,10 @@
         <v>171</v>
       </c>
       <c r="N462" t="n">
-        <v>345.26651452282</v>
+        <v>341.02145228216</v>
       </c>
       <c r="O462" t="n">
-        <v>59040.57398340222</v>
+        <v>58314.66834024936</v>
       </c>
       <c r="P462" t="n">
         <v>14500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -10846,10 +10846,10 @@
         <v>11066</v>
       </c>
       <c r="N234" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O234" t="n">
-        <v>7788191.456509088</v>
+        <v>7788191.437477118</v>
       </c>
       <c r="P234" t="n">
         <v>900</v>
@@ -20776,10 +20776,10 @@
         <v>80</v>
       </c>
       <c r="N443" t="n">
-        <v>4171.6683165468</v>
+        <v>4171.668314121</v>
       </c>
       <c r="O443" t="n">
-        <v>333733.465323744</v>
+        <v>333733.46512968</v>
       </c>
       <c r="P443" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -959,22 +959,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N14" t="n">
         <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>3618000</v>
+        <v>3591000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
       </c>
       <c r="Q14" t="n">
-        <v>2680000</v>
+        <v>2660000</v>
       </c>
     </row>
     <row r="15">
@@ -6976,22 +6976,22 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M151" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
         <v>12981.59</v>
       </c>
       <c r="O151" t="n">
-        <v>129815.9</v>
+        <v>0</v>
       </c>
       <c r="P151" t="n">
         <v>21900</v>
       </c>
       <c r="Q151" t="n">
-        <v>219000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8049,22 +8049,22 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M174" t="n">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="N174" t="n">
         <v>7635</v>
       </c>
       <c r="O174" t="n">
-        <v>2916570</v>
+        <v>2748600</v>
       </c>
       <c r="P174" t="n">
         <v>13900</v>
       </c>
       <c r="Q174" t="n">
-        <v>5309800</v>
+        <v>5004000</v>
       </c>
     </row>
     <row r="175">
@@ -12231,22 +12231,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M263" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="N263" t="n">
         <v>5798.41</v>
       </c>
       <c r="O263" t="n">
-        <v>179750.71</v>
+        <v>133363.43</v>
       </c>
       <c r="P263" t="n">
         <v>14900</v>
       </c>
       <c r="Q263" t="n">
-        <v>461900</v>
+        <v>342700</v>
       </c>
     </row>
     <row r="264">
@@ -12277,22 +12277,22 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N264" t="n">
         <v>52454.27</v>
       </c>
       <c r="O264" t="n">
-        <v>629451.24</v>
+        <v>576996.97</v>
       </c>
       <c r="P264" t="n">
         <v>88500</v>
       </c>
       <c r="Q264" t="n">
-        <v>1062000</v>
+        <v>973500</v>
       </c>
     </row>
     <row r="265">
@@ -13150,22 +13150,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M282" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N282" t="n">
         <v>7821.45</v>
       </c>
       <c r="O282" t="n">
-        <v>250286.4</v>
+        <v>203357.7</v>
       </c>
       <c r="P282" t="n">
         <v>12500</v>
       </c>
       <c r="Q282" t="n">
-        <v>400000</v>
+        <v>325000</v>
       </c>
     </row>
     <row r="283">
@@ -14606,22 +14606,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M312" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N312" t="n">
         <v>13377.81</v>
       </c>
       <c r="O312" t="n">
-        <v>107022.48</v>
+        <v>0</v>
       </c>
       <c r="P312" t="n">
         <v>36900</v>
       </c>
       <c r="Q312" t="n">
-        <v>295200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -556,10 +556,10 @@
         <v>269</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>7263000</v>
+        <v>7280671.532846733</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -926,10 +926,10 @@
         <v>92</v>
       </c>
       <c r="N13" t="n">
-        <v>27000</v>
+        <v>27267.326732673</v>
       </c>
       <c r="O13" t="n">
-        <v>2484000</v>
+        <v>2508594.059405916</v>
       </c>
       <c r="P13" t="n">
         <v>20000</v>
@@ -965,10 +965,10 @@
         <v>133</v>
       </c>
       <c r="N14" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O14" t="n">
-        <v>3591000</v>
+        <v>3611202.531645541</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
@@ -1043,10 +1043,10 @@
         <v>23</v>
       </c>
       <c r="N16" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O16" t="n">
-        <v>90317.2526359831</v>
+        <v>90317.252530121</v>
       </c>
       <c r="P16" t="n">
         <v>4800</v>
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O72" t="n">
-        <v>2329193.840875</v>
+        <v>2329193.828657951</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -4056,10 +4056,10 @@
         <v>273</v>
       </c>
       <c r="N84" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O84" t="n">
-        <v>4046509.417042638</v>
+        <v>4046509.416244659</v>
       </c>
       <c r="P84" t="n">
         <v>24900</v>
@@ -4367,10 +4367,10 @@
         <v>317</v>
       </c>
       <c r="N91" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O91" t="n">
-        <v>1385661.831141395</v>
+        <v>1385661.83159423</v>
       </c>
       <c r="P91" t="n">
         <v>8900</v>
@@ -4500,10 +4500,10 @@
         <v>166</v>
       </c>
       <c r="N94" t="n">
-        <v>1592.5645263158</v>
+        <v>1592.5644086022</v>
       </c>
       <c r="O94" t="n">
-        <v>264365.7113684228</v>
+        <v>264365.6918279652</v>
       </c>
       <c r="P94" t="n">
         <v>3900</v>
@@ -5088,10 +5088,10 @@
         <v>636</v>
       </c>
       <c r="N107" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O107" t="n">
-        <v>1037268.258171298</v>
+        <v>1037268.306214992</v>
       </c>
       <c r="P107" t="n">
         <v>2500</v>
@@ -5134,10 +5134,10 @@
         <v>23</v>
       </c>
       <c r="N108" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O108" t="n">
-        <v>35654.4834409887</v>
+        <v>35654.4836524645</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -5965,10 +5965,10 @@
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O127" t="n">
-        <v>4059.7484507042</v>
+        <v>4059.7485082246</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6047,10 +6047,10 @@
         <v>141</v>
       </c>
       <c r="N129" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O129" t="n">
-        <v>377984.2967376327</v>
+        <v>377984.2967105325</v>
       </c>
       <c r="P129" t="n">
         <v>4900</v>
@@ -6252,10 +6252,10 @@
         <v>27</v>
       </c>
       <c r="N134" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O134" t="n">
-        <v>29862</v>
+        <v>30001.4334630342</v>
       </c>
       <c r="P134" t="n">
         <v>2100</v>
@@ -6298,10 +6298,10 @@
         <v>4</v>
       </c>
       <c r="N135" t="n">
-        <v>11562.038395415</v>
+        <v>11562.038381503</v>
       </c>
       <c r="O135" t="n">
-        <v>46248.15358166</v>
+        <v>46248.153526012</v>
       </c>
       <c r="P135" t="n">
         <v>18500</v>
@@ -6423,22 +6423,22 @@
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
         <v>12214</v>
       </c>
       <c r="O138" t="n">
-        <v>73284</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
         <v>20900</v>
       </c>
       <c r="Q138" t="n">
-        <v>125400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6644,10 +6644,10 @@
         <v>19</v>
       </c>
       <c r="N143" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O143" t="n">
-        <v>510226</v>
+        <v>514537.769014092</v>
       </c>
       <c r="P143" t="n">
         <v>43900</v>
@@ -6726,10 +6726,10 @@
         <v>26</v>
       </c>
       <c r="N145" t="n">
-        <v>2568.8354081633</v>
+        <v>2568.8353767123</v>
       </c>
       <c r="O145" t="n">
-        <v>66789.7206122458</v>
+        <v>66789.7197945198</v>
       </c>
       <c r="P145" t="n">
         <v>4500</v>
@@ -7963,10 +7963,10 @@
         <v>153</v>
       </c>
       <c r="N172" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O172" t="n">
-        <v>2075445</v>
+        <v>2078657.763157836</v>
       </c>
       <c r="P172" t="n">
         <v>22500</v>
@@ -8147,10 +8147,10 @@
         <v>48</v>
       </c>
       <c r="N176" t="n">
-        <v>16086</v>
+        <v>16443.466666667</v>
       </c>
       <c r="O176" t="n">
-        <v>772128</v>
+        <v>789286.400000016</v>
       </c>
       <c r="P176" t="n">
         <v>25900</v>
@@ -8193,10 +8193,10 @@
         <v>67</v>
       </c>
       <c r="N177" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O177" t="n">
-        <v>1273536</v>
+        <v>1276964.091520829</v>
       </c>
       <c r="P177" t="n">
         <v>30900</v>
@@ -8331,10 +8331,10 @@
         <v>344</v>
       </c>
       <c r="N180" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O180" t="n">
-        <v>5874140.393431416</v>
+        <v>5886533.094683687</v>
       </c>
       <c r="P180" t="n">
         <v>27500</v>
@@ -8791,10 +8791,10 @@
         <v>36</v>
       </c>
       <c r="N190" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O190" t="n">
-        <v>119037.3936305724</v>
+        <v>119037.3933014352</v>
       </c>
       <c r="P190" t="n">
         <v>4900</v>
@@ -8883,10 +8883,10 @@
         <v>192</v>
       </c>
       <c r="N192" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O192" t="n">
-        <v>394767.6022353984</v>
+        <v>394767.554006976</v>
       </c>
       <c r="P192" t="n">
         <v>2900</v>
@@ -8975,10 +8975,10 @@
         <v>233</v>
       </c>
       <c r="N194" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O194" t="n">
-        <v>385831.4076043728</v>
+        <v>385831.4054847951</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9021,10 +9021,10 @@
         <v>1</v>
       </c>
       <c r="N195" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="O195" t="n">
-        <v>1592.2874455446</v>
+        <v>1592.2885084034</v>
       </c>
       <c r="P195" t="n">
         <v>2500</v>
@@ -9242,10 +9242,10 @@
         <v>192</v>
       </c>
       <c r="N200" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O200" t="n">
-        <v>132893.2837602471</v>
+        <v>132893.2869539712</v>
       </c>
       <c r="P200" t="n">
         <v>1200</v>
@@ -10088,10 +10088,10 @@
         <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="O218" t="n">
-        <v>1690.8700095969</v>
+        <v>1690.8700097561</v>
       </c>
       <c r="P218" t="n">
         <v>3000</v>
@@ -10474,10 +10474,10 @@
         <v>59</v>
       </c>
       <c r="N226" t="n">
-        <v>3259.1346835443</v>
+        <v>3259.1347844828</v>
       </c>
       <c r="O226" t="n">
-        <v>192288.9463291137</v>
+        <v>192288.9522844852</v>
       </c>
       <c r="P226" t="n">
         <v>3600</v>
@@ -10523,10 +10523,10 @@
         <v>378</v>
       </c>
       <c r="N227" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O227" t="n">
-        <v>1175895.725406746</v>
+        <v>1175895.697358504</v>
       </c>
       <c r="P227" t="n">
         <v>4500</v>
@@ -10751,10 +10751,10 @@
         <v>11066</v>
       </c>
       <c r="N232" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O232" t="n">
-        <v>7788190.989099176</v>
+        <v>7788190.961706952</v>
       </c>
       <c r="P232" t="n">
         <v>900</v>
@@ -11030,10 +11030,10 @@
         <v>59</v>
       </c>
       <c r="N238" t="n">
-        <v>2501.384</v>
+        <v>2501.3837931034</v>
       </c>
       <c r="O238" t="n">
-        <v>147581.656</v>
+        <v>147581.6437931006</v>
       </c>
       <c r="P238" t="n">
         <v>4100</v>
@@ -11903,10 +11903,10 @@
         <v>5</v>
       </c>
       <c r="N256" t="n">
-        <v>2832.195862069</v>
+        <v>2986.6792727273</v>
       </c>
       <c r="O256" t="n">
-        <v>14160.979310345</v>
+        <v>14933.3963636365</v>
       </c>
       <c r="P256" t="n">
         <v>12900</v>
@@ -12574,10 +12574,10 @@
         <v>5</v>
       </c>
       <c r="N270" t="n">
-        <v>12448.354</v>
+        <v>12448.355263158</v>
       </c>
       <c r="O270" t="n">
-        <v>62241.77</v>
+        <v>62241.77631579</v>
       </c>
       <c r="P270" t="n">
         <v>22900</v>
@@ -13352,10 +13352,10 @@
         <v>60</v>
       </c>
       <c r="N286" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O286" t="n">
-        <v>184025.437762236</v>
+        <v>185976.237455832</v>
       </c>
       <c r="P286" t="n">
         <v>7200</v>
@@ -14223,10 +14223,10 @@
         <v>1</v>
       </c>
       <c r="N304" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="O304" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="P304" t="n">
         <v>18900</v>
@@ -14517,10 +14517,10 @@
         <v>19</v>
       </c>
       <c r="N310" t="n">
-        <v>15347.45</v>
+        <v>15516.103296703</v>
       </c>
       <c r="O310" t="n">
-        <v>291601.55</v>
+        <v>294805.962637357</v>
       </c>
       <c r="P310" t="n">
         <v>23900</v>
@@ -15127,10 +15127,10 @@
         <v>159</v>
       </c>
       <c r="N323" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O323" t="n">
-        <v>829487.1</v>
+        <v>835412.0078571475</v>
       </c>
       <c r="P323" t="n">
         <v>20500</v>
@@ -16444,10 +16444,10 @@
         <v>984</v>
       </c>
       <c r="N350" t="n">
-        <v>430.60997520149</v>
+        <v>430.6099751861</v>
       </c>
       <c r="O350" t="n">
-        <v>423720.2155982662</v>
+        <v>423720.2155831224</v>
       </c>
       <c r="P350" t="n">
         <v>2200</v>
@@ -16817,10 +16817,10 @@
         <v>13</v>
       </c>
       <c r="N358" t="n">
-        <v>22951.704647137</v>
+        <v>22951.704432133</v>
       </c>
       <c r="O358" t="n">
-        <v>298372.160412781</v>
+        <v>298372.157617729</v>
       </c>
       <c r="P358" t="n">
         <v>37900</v>
@@ -18677,10 +18677,10 @@
         <v>165</v>
       </c>
       <c r="N398" t="n">
-        <v>9240</v>
+        <v>9401.162790697699</v>
       </c>
       <c r="O398" t="n">
-        <v>1524600</v>
+        <v>1551191.86046512</v>
       </c>
       <c r="P398" t="n">
         <v>11500</v>
@@ -20494,10 +20494,10 @@
         <v>570</v>
       </c>
       <c r="N437" t="n">
-        <v>2539.5719057816</v>
+        <v>2539.5719098712</v>
       </c>
       <c r="O437" t="n">
-        <v>1447555.986295512</v>
+        <v>1447555.988626584</v>
       </c>
       <c r="P437" t="n">
         <v>2900</v>
@@ -20586,10 +20586,10 @@
         <v>80</v>
       </c>
       <c r="N439" t="n">
-        <v>4171.6683018868</v>
+        <v>4171.6682869693</v>
       </c>
       <c r="O439" t="n">
-        <v>333733.464150944</v>
+        <v>333733.462957544</v>
       </c>
       <c r="P439" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O72" t="n">
-        <v>2329193.79535106</v>
+        <v>2332899.719490866</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -5134,10 +5134,10 @@
         <v>23</v>
       </c>
       <c r="N108" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O108" t="n">
-        <v>35654.4850620103</v>
+        <v>35654.4841388064</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -5965,10 +5965,10 @@
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O127" t="n">
-        <v>4059.7485082246</v>
+        <v>4059.7485227272</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6603,10 +6603,10 @@
         <v>19</v>
       </c>
       <c r="N142" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O142" t="n">
-        <v>514537.769014092</v>
+        <v>510226</v>
       </c>
       <c r="P142" t="n">
         <v>43900</v>
@@ -7594,10 +7594,10 @@
         <v>5</v>
       </c>
       <c r="N164" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O164" t="n">
-        <v>45944.89999999999</v>
+        <v>47281.47890909101</v>
       </c>
       <c r="P164" t="n">
         <v>12900</v>
@@ -7922,10 +7922,10 @@
         <v>153</v>
       </c>
       <c r="N171" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O171" t="n">
-        <v>2078657.763157836</v>
+        <v>2075445</v>
       </c>
       <c r="P171" t="n">
         <v>22500</v>
@@ -8106,10 +8106,10 @@
         <v>48</v>
       </c>
       <c r="N175" t="n">
-        <v>16443.466666667</v>
+        <v>16086</v>
       </c>
       <c r="O175" t="n">
-        <v>789286.400000016</v>
+        <v>772128</v>
       </c>
       <c r="P175" t="n">
         <v>25900</v>
@@ -8152,10 +8152,10 @@
         <v>67</v>
       </c>
       <c r="N176" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O176" t="n">
-        <v>1276964.091520829</v>
+        <v>1273536</v>
       </c>
       <c r="P176" t="n">
         <v>30900</v>
@@ -8290,10 +8290,10 @@
         <v>344</v>
       </c>
       <c r="N179" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O179" t="n">
-        <v>5886533.094683687</v>
+        <v>5874140.393080192</v>
       </c>
       <c r="P179" t="n">
         <v>27500</v>
@@ -8520,10 +8520,10 @@
         <v>552</v>
       </c>
       <c r="N184" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O184" t="n">
-        <v>836853.3609396841</v>
+        <v>836853.3618516432</v>
       </c>
       <c r="P184" t="n">
         <v>2300</v>
@@ -8704,10 +8704,10 @@
         <v>74</v>
       </c>
       <c r="N188" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O188" t="n">
-        <v>133423.3032240714</v>
+        <v>133423.3062753948</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8796,10 +8796,10 @@
         <v>264</v>
       </c>
       <c r="N190" t="n">
-        <v>2122.1634163581</v>
+        <v>2122.1634141414</v>
       </c>
       <c r="O190" t="n">
-        <v>560251.1419185385</v>
+        <v>560251.1413333296</v>
       </c>
       <c r="P190" t="n">
         <v>2900</v>
@@ -8888,10 +8888,10 @@
         <v>162</v>
       </c>
       <c r="N192" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O192" t="n">
-        <v>522380.3454484325</v>
+        <v>522380.3463600714</v>
       </c>
       <c r="P192" t="n">
         <v>4500</v>
@@ -8934,10 +8934,10 @@
         <v>233</v>
       </c>
       <c r="N193" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O193" t="n">
-        <v>385831.4054847951</v>
+        <v>385831.3667352874</v>
       </c>
       <c r="P193" t="n">
         <v>2500</v>
@@ -8980,10 +8980,10 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="O194" t="n">
-        <v>1592.2886257928</v>
+        <v>1592.2887446809</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9070,10 +9070,10 @@
         <v>600</v>
       </c>
       <c r="N196" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O196" t="n">
-        <v>755565.12055644</v>
+        <v>755565.10615386</v>
       </c>
       <c r="P196" t="n">
         <v>1900</v>
@@ -9201,10 +9201,10 @@
         <v>192</v>
       </c>
       <c r="N199" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O199" t="n">
-        <v>132893.2880279367</v>
+        <v>132893.2891066502</v>
       </c>
       <c r="P199" t="n">
         <v>1200</v>
@@ -9489,10 +9489,10 @@
         <v>31</v>
       </c>
       <c r="N205" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O205" t="n">
-        <v>277306.78</v>
+        <v>277431.7868129222</v>
       </c>
       <c r="P205" t="n">
         <v>14900</v>
@@ -10710,10 +10710,10 @@
         <v>11066</v>
       </c>
       <c r="N231" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O231" t="n">
-        <v>7788190.91815007</v>
+        <v>7788190.937516455</v>
       </c>
       <c r="P231" t="n">
         <v>900</v>
@@ -11862,10 +11862,10 @@
         <v>5</v>
       </c>
       <c r="N255" t="n">
-        <v>2986.6792727273</v>
+        <v>2832.1961818182</v>
       </c>
       <c r="O255" t="n">
-        <v>14933.3963636365</v>
+        <v>14160.980909091</v>
       </c>
       <c r="P255" t="n">
         <v>12900</v>
@@ -14182,10 +14182,10 @@
         <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="O303" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="P303" t="n">
         <v>18900</v>
@@ -15086,10 +15086,10 @@
         <v>159</v>
       </c>
       <c r="N322" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O322" t="n">
-        <v>835412.0078571475</v>
+        <v>829487.1</v>
       </c>
       <c r="P322" t="n">
         <v>20500</v>
@@ -16452,10 +16452,10 @@
         <v>726</v>
       </c>
       <c r="N350" t="n">
-        <v>465.87103377687</v>
+        <v>465.87103696099</v>
       </c>
       <c r="O350" t="n">
-        <v>338222.3705220076</v>
+        <v>338222.3728336787</v>
       </c>
       <c r="P350" t="n">
         <v>2500</v>
@@ -16776,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="N357" t="n">
-        <v>22951.704393305</v>
+        <v>22951.704377622</v>
       </c>
       <c r="O357" t="n">
-        <v>298372.157112965</v>
+        <v>298372.156909086</v>
       </c>
       <c r="P357" t="n">
         <v>37900</v>
@@ -19898,10 +19898,10 @@
         <v>42</v>
       </c>
       <c r="N424" t="n">
-        <v>2432.1360526316</v>
+        <v>2432.1363013699</v>
       </c>
       <c r="O424" t="n">
-        <v>102149.7142105272</v>
+        <v>102149.7246575358</v>
       </c>
       <c r="P424" t="n">
         <v>4500</v>
@@ -20499,10 +20499,10 @@
         <v>561</v>
       </c>
       <c r="N437" t="n">
-        <v>4687.9754746137</v>
+        <v>4719.2286444444</v>
       </c>
       <c r="O437" t="n">
-        <v>2629954.241258285</v>
+        <v>2647487.269533308</v>
       </c>
       <c r="P437" t="n">
         <v>5500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2586.3633253779</v>
+        <v>2582.2547091633</v>
       </c>
       <c r="O72" t="n">
-        <v>2332899.719490866</v>
+        <v>2329193.747665297</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3541,10 +3541,10 @@
         <v>1309</v>
       </c>
       <c r="N73" t="n">
-        <v>5216.8958101422</v>
+        <v>5216.8958023544</v>
       </c>
       <c r="O73" t="n">
-        <v>6828916.615476141</v>
+        <v>6828916.60528191</v>
       </c>
       <c r="P73" t="n">
         <v>8500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608436687</v>
+        <v>3158.8608437109</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.47691027</v>
+        <v>10771715.47705417</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -4500,10 +4500,10 @@
         <v>166</v>
       </c>
       <c r="N94" t="n">
-        <v>1592.5643478261</v>
+        <v>1592.564335512</v>
       </c>
       <c r="O94" t="n">
-        <v>264365.6817391326</v>
+        <v>264365.679694992</v>
       </c>
       <c r="P94" t="n">
         <v>3900</v>
@@ -5088,10 +5088,10 @@
         <v>636</v>
       </c>
       <c r="N107" t="n">
-        <v>1630.9251181364</v>
+        <v>1630.9251335113</v>
       </c>
       <c r="O107" t="n">
-        <v>1037268.37513475</v>
+        <v>1037268.384913187</v>
       </c>
       <c r="P107" t="n">
         <v>2500</v>
@@ -5837,10 +5837,10 @@
         <v>109</v>
       </c>
       <c r="N124" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O124" t="n">
-        <v>457459.1075984314</v>
+        <v>457459.1082199821</v>
       </c>
       <c r="P124" t="n">
         <v>5900</v>
@@ -6047,10 +6047,10 @@
         <v>141</v>
       </c>
       <c r="N129" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O129" t="n">
-        <v>377984.2967105325</v>
+        <v>377984.2966562051</v>
       </c>
       <c r="P129" t="n">
         <v>4900</v>
@@ -6088,10 +6088,10 @@
         <v>402</v>
       </c>
       <c r="N130" t="n">
-        <v>880.32993798065</v>
+        <v>880.329947852</v>
       </c>
       <c r="O130" t="n">
-        <v>353892.6350682213</v>
+        <v>353892.639036504</v>
       </c>
       <c r="P130" t="n">
         <v>1200</v>
@@ -6298,10 +6298,10 @@
         <v>4</v>
       </c>
       <c r="N135" t="n">
-        <v>11562.038381503</v>
+        <v>11562.038362573</v>
       </c>
       <c r="O135" t="n">
-        <v>46248.153526012</v>
+        <v>46248.153450292</v>
       </c>
       <c r="P135" t="n">
         <v>18500</v>
@@ -7594,10 +7594,10 @@
         <v>5</v>
       </c>
       <c r="N164" t="n">
-        <v>9456.2957818182</v>
+        <v>9188.98</v>
       </c>
       <c r="O164" t="n">
-        <v>47281.47890909101</v>
+        <v>45944.89999999999</v>
       </c>
       <c r="P164" t="n">
         <v>12900</v>
@@ -8520,10 +8520,10 @@
         <v>552</v>
       </c>
       <c r="N184" t="n">
-        <v>1516.0386990066</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O184" t="n">
-        <v>836853.3618516432</v>
+        <v>836853.3609396841</v>
       </c>
       <c r="P184" t="n">
         <v>2300</v>
@@ -8566,10 +8566,10 @@
         <v>312</v>
       </c>
       <c r="N185" t="n">
-        <v>2458.5122658275</v>
+        <v>2458.5122572276</v>
       </c>
       <c r="O185" t="n">
-        <v>767055.82693818</v>
+        <v>767055.8242550112</v>
       </c>
       <c r="P185" t="n">
         <v>3500</v>
@@ -8704,10 +8704,10 @@
         <v>74</v>
       </c>
       <c r="N188" t="n">
-        <v>1803.0176523702</v>
+        <v>1803.0176696833</v>
       </c>
       <c r="O188" t="n">
-        <v>133423.3062753948</v>
+        <v>133423.3075565642</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8842,10 +8842,10 @@
         <v>192</v>
       </c>
       <c r="N191" t="n">
-        <v>2056.081010453</v>
+        <v>2056.0810065359</v>
       </c>
       <c r="O191" t="n">
-        <v>394767.554006976</v>
+        <v>394767.5532548928</v>
       </c>
       <c r="P191" t="n">
         <v>2900</v>
@@ -8980,10 +8980,10 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>1592.2887446809</v>
+        <v>1592.2892358079</v>
       </c>
       <c r="O194" t="n">
-        <v>1592.2887446809</v>
+        <v>1592.2892358079</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9070,10 +9070,10 @@
         <v>600</v>
       </c>
       <c r="N196" t="n">
-        <v>1259.2751769231</v>
+        <v>1259.2751809084</v>
       </c>
       <c r="O196" t="n">
-        <v>755565.10615386</v>
+        <v>755565.10854504</v>
       </c>
       <c r="P196" t="n">
         <v>1900</v>
@@ -9201,10 +9201,10 @@
         <v>192</v>
       </c>
       <c r="N199" t="n">
-        <v>692.15254743047</v>
+        <v>692.15255307366</v>
       </c>
       <c r="O199" t="n">
-        <v>132893.2891066502</v>
+        <v>132893.2901901427</v>
       </c>
       <c r="P199" t="n">
         <v>1200</v>
@@ -9489,10 +9489,10 @@
         <v>31</v>
       </c>
       <c r="N205" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O205" t="n">
-        <v>277431.7868129222</v>
+        <v>277306.78</v>
       </c>
       <c r="P205" t="n">
         <v>14900</v>
@@ -10047,10 +10047,10 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>1690.8700097895</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="O217" t="n">
-        <v>1690.8700097895</v>
+        <v>1690.8700098184</v>
       </c>
       <c r="P217" t="n">
         <v>3000</v>
@@ -10710,10 +10710,10 @@
         <v>11066</v>
       </c>
       <c r="N231" t="n">
-        <v>703.7945904135599</v>
+        <v>703.79458486774</v>
       </c>
       <c r="O231" t="n">
-        <v>7788190.937516455</v>
+        <v>7788190.876146411</v>
       </c>
       <c r="P231" t="n">
         <v>900</v>
@@ -14182,10 +14182,10 @@
         <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>19429.807619048</v>
+        <v>10737.525135135</v>
       </c>
       <c r="O303" t="n">
-        <v>19429.807619048</v>
+        <v>10737.525135135</v>
       </c>
       <c r="P303" t="n">
         <v>18900</v>
@@ -17619,10 +17619,10 @@
         <v>1427</v>
       </c>
       <c r="N375" t="n">
-        <v>219.99758867125</v>
+        <v>219.9969793366</v>
       </c>
       <c r="O375" t="n">
-        <v>313936.5590338738</v>
+        <v>313935.6895133282</v>
       </c>
       <c r="P375" t="n">
         <v>260</v>
@@ -19510,10 +19510,10 @@
         <v>8</v>
       </c>
       <c r="N416" t="n">
-        <v>1319.3610989011</v>
+        <v>1319.3611070111</v>
       </c>
       <c r="O416" t="n">
-        <v>10554.8887912088</v>
+        <v>10554.8888560888</v>
       </c>
       <c r="P416" t="n">
         <v>3500</v>
@@ -20499,10 +20499,10 @@
         <v>561</v>
       </c>
       <c r="N437" t="n">
-        <v>4719.2286444444</v>
+        <v>4687.9755111111</v>
       </c>
       <c r="O437" t="n">
-        <v>2647487.269533308</v>
+        <v>2629954.261733327</v>
       </c>
       <c r="P437" t="n">
         <v>5500</v>
@@ -20545,10 +20545,10 @@
         <v>80</v>
       </c>
       <c r="N438" t="n">
-        <v>4171.6682692308</v>
+        <v>4171.6682164634</v>
       </c>
       <c r="O438" t="n">
-        <v>333733.4615384641</v>
+        <v>333733.457317072</v>
       </c>
       <c r="P438" t="n">
         <v>5000</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -1277,10 +1277,10 @@
         <v>38</v>
       </c>
       <c r="N22" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O22" t="n">
-        <v>810680.22</v>
+        <v>814159.534248944</v>
       </c>
       <c r="P22" t="n">
         <v>30000</v>
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O72" t="n">
-        <v>2329193.747665297</v>
+        <v>2329193.726019191</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -4056,10 +4056,10 @@
         <v>273</v>
       </c>
       <c r="N84" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O84" t="n">
-        <v>4046509.416244659</v>
+        <v>4049010.34913466</v>
       </c>
       <c r="P84" t="n">
         <v>24900</v>
@@ -4367,10 +4367,10 @@
         <v>317</v>
       </c>
       <c r="N91" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O91" t="n">
-        <v>1385661.832501198</v>
+        <v>1385661.832652534</v>
       </c>
       <c r="P91" t="n">
         <v>8900</v>
@@ -5088,10 +5088,10 @@
         <v>636</v>
       </c>
       <c r="N107" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O107" t="n">
-        <v>1037268.384913187</v>
+        <v>1038655.107352952</v>
       </c>
       <c r="P107" t="n">
         <v>2500</v>
@@ -5134,10 +5134,10 @@
         <v>23</v>
       </c>
       <c r="N108" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O108" t="n">
-        <v>35654.4841388064</v>
+        <v>35654.4841693412</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -7594,10 +7594,10 @@
         <v>5</v>
       </c>
       <c r="N164" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O164" t="n">
-        <v>45944.89999999999</v>
+        <v>46271.909964413</v>
       </c>
       <c r="P164" t="n">
         <v>12900</v>
@@ -8520,10 +8520,10 @@
         <v>552</v>
       </c>
       <c r="N184" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O184" t="n">
-        <v>836853.3609396841</v>
+        <v>836853.3608635631</v>
       </c>
       <c r="P184" t="n">
         <v>2300</v>
@@ -8704,10 +8704,10 @@
         <v>74</v>
       </c>
       <c r="N188" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O188" t="n">
-        <v>133423.3075565642</v>
+        <v>133423.3078134922</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8750,10 +8750,10 @@
         <v>36</v>
       </c>
       <c r="N189" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O189" t="n">
-        <v>119037.3936305724</v>
+        <v>119037.3929712468</v>
       </c>
       <c r="P189" t="n">
         <v>4900</v>
@@ -8980,10 +8980,10 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="O194" t="n">
-        <v>1592.2892358079</v>
+        <v>1595.7734573304</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9070,10 +9070,10 @@
         <v>600</v>
       </c>
       <c r="N196" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O196" t="n">
-        <v>755565.10854504</v>
+        <v>755565.10934292</v>
       </c>
       <c r="P196" t="n">
         <v>1900</v>
@@ -10710,10 +10710,10 @@
         <v>11066</v>
       </c>
       <c r="N231" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O231" t="n">
-        <v>7788190.876146411</v>
+        <v>7788190.856740187</v>
       </c>
       <c r="P231" t="n">
         <v>900</v>
@@ -14182,10 +14182,10 @@
         <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="O303" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="P303" t="n">
         <v>18900</v>
@@ -16776,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="N357" t="n">
-        <v>22951.704377622</v>
+        <v>22951.704345992</v>
       </c>
       <c r="O357" t="n">
-        <v>298372.156909086</v>
+        <v>298372.156497896</v>
       </c>
       <c r="P357" t="n">
         <v>37900</v>
@@ -18492,10 +18492,10 @@
         <v>47</v>
       </c>
       <c r="N394" t="n">
-        <v>7920</v>
+        <v>7953.8461538462</v>
       </c>
       <c r="O394" t="n">
-        <v>372240</v>
+        <v>373830.7692307714</v>
       </c>
       <c r="P394" t="n">
         <v>10500</v>
@@ -18590,10 +18590,10 @@
         <v>37</v>
       </c>
       <c r="N396" t="n">
-        <v>7920</v>
+        <v>7971.0967741935</v>
       </c>
       <c r="O396" t="n">
-        <v>293040</v>
+        <v>294930.5806451595</v>
       </c>
       <c r="P396" t="n">
         <v>10500</v>

--- a/bodegas/03.xlsx
+++ b/bodegas/03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1121,10 +1121,10 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2474.7033461538</v>
+        <v>2474.7028512397</v>
       </c>
       <c r="O18" t="n">
-        <v>9898.8133846152</v>
+        <v>9898.8114049588</v>
       </c>
       <c r="P18" t="n">
         <v>4500</v>
@@ -1238,10 +1238,10 @@
         <v>67</v>
       </c>
       <c r="N21" t="n">
-        <v>27000</v>
+        <v>27051.823416507</v>
       </c>
       <c r="O21" t="n">
-        <v>1809000</v>
+        <v>1812472.168905969</v>
       </c>
       <c r="P21" t="n">
         <v>30000</v>
@@ -1277,10 +1277,10 @@
         <v>38</v>
       </c>
       <c r="N22" t="n">
-        <v>21425.250901288</v>
+        <v>21333.69</v>
       </c>
       <c r="O22" t="n">
-        <v>814159.534248944</v>
+        <v>810680.22</v>
       </c>
       <c r="P22" t="n">
         <v>30000</v>
@@ -1316,10 +1316,10 @@
         <v>30</v>
       </c>
       <c r="N23" t="n">
-        <v>15403.521104651</v>
+        <v>15403.521169591</v>
       </c>
       <c r="O23" t="n">
-        <v>462105.63313953</v>
+        <v>462105.63508773</v>
       </c>
       <c r="P23" t="n">
         <v>33500</v>
@@ -2241,10 +2241,10 @@
         <v>23</v>
       </c>
       <c r="N44" t="n">
-        <v>27000</v>
+        <v>27118.421052632</v>
       </c>
       <c r="O44" t="n">
-        <v>621000</v>
+        <v>623723.684210536</v>
       </c>
       <c r="P44" t="n">
         <v>20000</v>
@@ -3098,10 +3098,10 @@
         <v>33</v>
       </c>
       <c r="N63" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O63" t="n">
-        <v>162931.2362317596</v>
+        <v>162931.2362371122</v>
       </c>
       <c r="P63" t="n">
         <v>7500</v>
@@ -3495,10 +3495,10 @@
         <v>902</v>
       </c>
       <c r="N72" t="n">
-        <v>2582.2546851654</v>
+        <v>2582.2546595174</v>
       </c>
       <c r="O72" t="n">
-        <v>2329193.726019191</v>
+        <v>2329193.702884695</v>
       </c>
       <c r="P72" t="n">
         <v>4500</v>
@@ -3633,10 +3633,10 @@
         <v>3410</v>
       </c>
       <c r="N75" t="n">
-        <v>3158.8608437109</v>
+        <v>3158.8608442176</v>
       </c>
       <c r="O75" t="n">
-        <v>10771715.47705417</v>
+        <v>10771715.47878202</v>
       </c>
       <c r="P75" t="n">
         <v>5600</v>
@@ -4056,10 +4056,10 @@
         <v>273</v>
       </c>
       <c r="N84" t="n">
-        <v>14831.53974042</v>
+        <v>14822.378811881</v>
       </c>
       <c r="O84" t="n">
-        <v>4049010.34913466</v>
+        <v>4046509.415643513</v>
       </c>
       <c r="P84" t="n">
         <v>24900</v>
@@ -4367,10 +4367,10 @@
         <v>317</v>
       </c>
       <c r="N91" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O91" t="n">
-        <v>1385661.832652534</v>
+        <v>1385661.833561563</v>
       </c>
       <c r="P91" t="n">
         <v>8900</v>
@@ -5088,10 +5088,10 @@
         <v>636</v>
       </c>
       <c r="N107" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O107" t="n">
-        <v>1038655.107352952</v>
+        <v>1037268.456180103</v>
       </c>
       <c r="P107" t="n">
         <v>2500</v>
@@ -5134,10 +5134,10 @@
         <v>23</v>
       </c>
       <c r="N108" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O108" t="n">
-        <v>35654.4841693412</v>
+        <v>35654.4846755344</v>
       </c>
       <c r="P108" t="n">
         <v>2500</v>
@@ -5965,10 +5965,10 @@
         <v>2</v>
       </c>
       <c r="N127" t="n">
-        <v>2029.8742613636</v>
+        <v>2029.8742906178</v>
       </c>
       <c r="O127" t="n">
-        <v>4059.7485227272</v>
+        <v>4059.7485812356</v>
       </c>
       <c r="P127" t="n">
         <v>3600</v>
@@ -6298,10 +6298,10 @@
         <v>4</v>
       </c>
       <c r="N135" t="n">
-        <v>11562.038362573</v>
+        <v>11562.038338279</v>
       </c>
       <c r="O135" t="n">
-        <v>46248.153450292</v>
+        <v>46248.153353116</v>
       </c>
       <c r="P135" t="n">
         <v>18500</v>
@@ -8428,10 +8428,10 @@
         <v>66</v>
       </c>
       <c r="N182" t="n">
-        <v>10713.21</v>
+        <v>10736.550326797</v>
       </c>
       <c r="O182" t="n">
-        <v>707071.86</v>
+        <v>708612.321568602</v>
       </c>
       <c r="P182" t="n">
         <v>20900</v>
@@ -8520,10 +8520,10 @@
         <v>552</v>
       </c>
       <c r="N184" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O184" t="n">
-        <v>836853.3608635631</v>
+        <v>836853.3611678808</v>
       </c>
       <c r="P184" t="n">
         <v>2300</v>
@@ -8566,10 +8566,10 @@
         <v>312</v>
       </c>
       <c r="N185" t="n">
-        <v>2458.5122572276</v>
+        <v>2458.5121994025</v>
       </c>
       <c r="O185" t="n">
-        <v>767055.8242550112</v>
+        <v>767055.80621358</v>
       </c>
       <c r="P185" t="n">
         <v>3500</v>
@@ -8658,10 +8658,10 @@
         <v>216</v>
       </c>
       <c r="N187" t="n">
-        <v>2079.3831463696</v>
+        <v>2079.3831437356</v>
       </c>
       <c r="O187" t="n">
-        <v>449146.7596158336</v>
+        <v>449146.7590468896</v>
       </c>
       <c r="P187" t="n">
         <v>2900</v>
@@ -8704,10 +8704,10 @@
         <v>74</v>
       </c>
       <c r="N188" t="n">
-        <v>1803.0176731553</v>
+        <v>1803.0177185792</v>
       </c>
       <c r="O188" t="n">
-        <v>133423.3078134922</v>
+        <v>133423.3111748608</v>
       </c>
       <c r="P188" t="n">
         <v>2500</v>
@@ -8888,10 +8888,10 @@
         <v>162</v>
       </c>
       <c r="N192" t="n">
-        <v>3224.5700392597</v>
+        <v>3224.5700448934</v>
       </c>
       <c r="O192" t="n">
-        <v>522380.3463600714</v>
+        <v>522380.3472727308</v>
       </c>
       <c r="P192" t="n">
         <v>4500</v>
@@ -8980,10 +8980,10 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="O194" t="n">
-        <v>1595.7734573304</v>
+        <v>1592.2894481236</v>
       </c>
       <c r="P194" t="n">
         <v>2500</v>
@@ -9070,10 +9070,10 @@
         <v>600</v>
       </c>
       <c r="N196" t="n">
-        <v>1259.2751822382</v>
+        <v>1259.2752022675</v>
       </c>
       <c r="O196" t="n">
-        <v>755565.10934292</v>
+        <v>755565.1213605</v>
       </c>
       <c r="P196" t="n">
         <v>1900</v>
@@ -10047,10 +10047,10 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>1690.8700098184</v>
+        <v>1690.8700098765</v>
       </c>
       <c r="O217" t="n">
-        <v>1690.8700098184</v>
+        <v>1690.8700098765</v>
       </c>
       <c r="P217" t="n">
         <v>3000</v>
@@ -10145,10 +10145,10 @@
         <v>-2</v>
       </c>
       <c r="N219" t="n">
-        <v>2270.3215151515</v>
+        <v>2270.3217241379</v>
       </c>
       <c r="O219" t="n">
-        <v>-4540.643030303</v>
+        <v>-4540.6434482758</v>
       </c>
       <c r="P219" t="n">
         <v>3900</v>
@@ -10710,10 +10710,10 @@
         <v>11066</v>
       </c>
       <c r="N231" t="n">
-        <v>703.7945831140599</v>
+        <v>703.79457726026</v>
       </c>
       <c r="O231" t="n">
-        <v>7788190.856740187</v>
+        <v>7788190.791962037</v>
       </c>
       <c r="P231" t="n">
         <v>900</v>
@@ -10989,10 +10989,10 @@
         <v>59</v>
       </c>
       <c r="N237" t="n">
-        <v>2501.3837931034</v>
+        <v>2501.3837572254</v>
       </c>
       <c r="O237" t="n">
-        <v>147581.6437931006</v>
+        <v>147581.6416762986</v>
       </c>
       <c r="P237" t="n">
         <v>4100</v>
@@ -11862,10 +11862,10 @@
         <v>5</v>
       </c>
       <c r="N255" t="n">
-        <v>2832.1961818182</v>
+        <v>2832.1965384615</v>
       </c>
       <c r="O255" t="n">
-        <v>14160.980909091</v>
+        <v>14160.9826923075</v>
       </c>
       <c r="P255" t="n">
         <v>12900</v>
@@ -12922,10 +12922,10 @@
         <v>11</v>
       </c>
       <c r="N277" t="n">
-        <v>5430.86</v>
+        <v>5546.410212766</v>
       </c>
       <c r="O277" t="n">
-        <v>59739.46</v>
+        <v>61010.512340426</v>
       </c>
       <c r="P277" t="n">
         <v>13900</v>
@@ -14182,10 +14182,10 @@
         <v>1</v>
       </c>
       <c r="N303" t="n">
-        <v>10737.525</v>
+        <v>10737.524705882</v>
       </c>
       <c r="O303" t="n">
-        <v>10737.525</v>
+        <v>10737.524705882</v>
       </c>
       <c r="P303" t="n">
         <v>18900</v>
@@ -15720,10 +15720,10 @@
         <v>2</v>
       </c>
       <c r="N335" t="n">
-        <v>26378.02625</v>
+        <v>26378.025714286</v>
       </c>
       <c r="O335" t="n">
-        <v>52756.0525</v>
+        <v>52756.051428572</v>
       </c>
       <c r="P335" t="n">
         <v>36500</v>
@@ -16776,10 +16776,10 @@
         <v>13</v>
       </c>
       <c r="N357" t="n">
-        <v>22951.704345992</v>
+        <v>22951.704248927</v>
       </c>
       <c r="O357" t="n">
-        <v>298372.156497896</v>
+        <v>298372.155236051</v>
       </c>
       <c r="P357" t="n">
         <v>37900</v>
@@ -16919,10 +16919,10 @@
         <v>36</v>
       </c>
       <c r="N360" t="n">
-        <v>1547.8829824561</v>
+        <v>1547.8830909091</v>
       </c>
       <c r="O360" t="n">
-        <v>55723.7873684196</v>
+        <v>55723.7912727276</v>
       </c>
       <c r="P360" t="n">
         <v>5500</v>
@@ -18492,10 +18492,10 @@
         <v>47</v>
       </c>
       <c r="N394" t="n">
-        <v>7953.8461538462</v>
+        <v>7920</v>
       </c>
       <c r="O394" t="n">
-        <v>373830.7692307714</v>
+        <v>372240</v>
       </c>
       <c r="P394" t="n">
         <v>10500</v>
@@ -18590,10 +18590,10 @@
         <v>37</v>
       </c>
       <c r="N396" t="n">
-        <v>7971.0967741935</v>
+        <v>7920</v>
       </c>
       <c r="O396" t="n">
-        <v>294930.5806451595</v>
+        <v>293040</v>
       </c>
       <c r="P396" t="n">
         <v>10500</v>
@@ -19510,10 +19510,10 @@
         <v>8</v>
       </c>
       <c r="N416" t="n">
-        <v>1319.3611070111</v>
+        <v>1319.3612448133</v>
       </c>
       <c r="O416" t="n">
-        <v>10554.8888560888</v>
+        <v>10554.8899585064</v>
       </c>
       <c r="P416" t="n">
         <v>3500</v>
